--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,11 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="15">
@@ -145,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,6 +200,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6817,551 +6831,581 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="106" ht="45" customHeight="1">
+      <c r="A106" s="19" t="inlineStr">
         <is>
           <t>PERF-003</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="19" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="20" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="D106" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E106" t="inlineStr">
+      <c r="D106" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E106" s="19" t="inlineStr">
         <is>
           <t>대시보드 SQL 집계 전환 (ORM 전체 로드 → GROUP BY)</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G106" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="H106" s="19" t="n"/>
+      <c r="I106" s="19" t="inlineStr">
         <is>
           <t>dashboard summary/priority/category/assignee/rounds/heatmap가 전체 ORM 객체를 Python에서 카운팅</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J106" s="19" t="inlineStr">
         <is>
           <t>SQL CASE+GROUP BY 집계로 전면 전환. _get_all_results 제거, _latest_run_subquery/_result_count_cases 헬퍼 추가</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="K106" s="19" t="inlineStr">
         <is>
           <t>대시보드 전체</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="L106" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="45" customHeight="1">
+      <c r="A107" s="19" t="inlineStr">
         <is>
           <t>PERF-004</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="19" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="20" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="D107" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E107" t="inlineStr">
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
         <is>
           <t>Overview SQL 집계 전환 (Python 카운팅 → SQL 서브쿼리)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G107" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="H107" s="19" t="n"/>
+      <c r="I107" s="19" t="inlineStr">
         <is>
           <t>overview 엔드포인트가 전체 TestResult ORM 로드 후 Python _count_results로 집계</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J107" s="19" t="inlineStr">
         <is>
           <t>SQL CASE+서브쿼리 3회로 전환, _count_results 제거</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K107" s="19" t="inlineStr">
         <is>
           <t>글로벌 대시보드</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="L107" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="45" customHeight="1">
+      <c r="A108" s="19" t="inlineStr">
         <is>
           <t>PERF-005</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="20" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="D108" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E108" t="inlineStr">
+      <c r="D108" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E108" s="19" t="inlineStr">
         <is>
           <t>TestPlan 목록 N+1 제거 (플랜별 개별 조회 → SQL 2회)</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G108" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="H108" s="19" t="n"/>
+      <c r="I108" s="19" t="inlineStr">
         <is>
           <t>list_test_plans에서 플랜마다 run_count + _plan_progress 개별 DB 조회 (N+1)</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="J108" s="19" t="inlineStr">
         <is>
           <t>_bulk_plan_stats 추가, SQL CASE 집계 2회로 고정</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="K108" s="19" t="inlineStr">
         <is>
           <t>테스트 플랜 목록</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="L108" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="45" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
         <is>
           <t>PERF-006</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="20" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="D109" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E109" t="inlineStr">
+      <c r="D109" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="inlineStr">
         <is>
           <t>TestRun 생성/복제 bulk insert 적용</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G109" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="H109" s="19" t="n"/>
+      <c r="I109" s="19" t="inlineStr">
         <is>
           <t>create_testrun/clone에서 TC당 개별 db.add() — 5000건 시 ~7초</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J109" s="19" t="inlineStr">
         <is>
           <t>bulk_insert_mappings로 전환, TC ID만 select</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="K109" s="19" t="inlineStr">
         <is>
           <t>TestRun 생성/복제</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="L109" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="45" customHeight="1">
+      <c r="A110" s="19" t="inlineStr">
         <is>
           <t>PERF-007</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="19" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="20" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="D110" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E110" t="inlineStr">
+      <c r="D110" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E110" s="19" t="inlineStr">
         <is>
           <t>결과 제출 N+1 제거 (per-item .first() → IN prefetch)</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G110" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="H110" s="19" t="n"/>
+      <c r="I110" s="19" t="inlineStr">
         <is>
           <t>submit_results에서 결과마다 기존 레코드를 개별 .first()로 조회</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J110" s="19" t="inlineStr">
         <is>
           <t>IN 쿼리 1회로 일괄 prefetch, existing_map dict 구성</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K110" s="19" t="inlineStr">
         <is>
           <t>테스트 결과 제출</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="L110" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="45" customHeight="1">
+      <c r="A111" s="19" t="inlineStr">
         <is>
           <t>PERF-008</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="19" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="20" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="D111" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E111" t="inlineStr">
+      <c r="D111" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E111" s="19" t="inlineStr">
         <is>
           <t>리포트 SQL 집계 + 이중 로드 제거</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G111" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="H111" s="19" t="n"/>
+      <c r="I111" s="19" t="inlineStr">
         <is>
           <t>report Excel에서 _build_report_data + 별도 db.query 이중 로드, summary를 Python 카운팅</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="J111" s="19" t="inlineStr">
         <is>
           <t>_summary_sql/_category_summary_sql/_failed_items SQL 집계 헬퍼 추가, Excel은 결과 1회만 load_only 조회</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="K111" s="19" t="inlineStr">
         <is>
           <t>리포트 JSON/PDF/Excel</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="L111" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="45" customHeight="1">
+      <c r="A112" s="19" t="inlineStr">
         <is>
           <t>PERF-009</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="19" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="20" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
       </c>
-      <c r="D112" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E112" t="inlineStr">
+      <c r="D112" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E112" s="19" t="inlineStr">
         <is>
           <t>SQLite WAL 모드 활성화</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G112" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="H112" s="19" t="n"/>
+      <c r="I112" s="19" t="inlineStr">
         <is>
           <t>SQLite 기본 journal_mode=delete, 동시 읽기/쓰기 시 lock</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="J112" s="19" t="inlineStr">
         <is>
           <t>PRAGMA journal_mode=WAL 추가 (database.py)</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="K112" s="19" t="inlineStr">
         <is>
           <t>DB 전체</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="L112" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="45" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
         <is>
           <t>PERF-010</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="19" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="20" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
       </c>
-      <c r="D113" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E113" t="inlineStr">
+      <c r="D113" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E113" s="19" t="inlineStr">
         <is>
           <t>시트 트리 순회 N+1 제거 (_collect_descendant_names)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G113" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="H113" s="19" t="n"/>
+      <c r="I113" s="19" t="inlineStr">
         <is>
           <t>_collect_descendant_names에서 재귀 while 루프로 시트마다 개별 DB 조회</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="J113" s="19" t="inlineStr">
         <is>
           <t>전체 시트 1회 fetch 후 메모리 children_map DFS 탐색</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="K113" s="19" t="inlineStr">
         <is>
           <t>시트 이동/삭제</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="L113" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="45" customHeight="1">
+      <c r="A114" s="19" t="inlineStr">
         <is>
           <t>ENH-034</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="19" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="20" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
       </c>
-      <c r="D114" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E114" t="inlineStr">
+      <c r="D114" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E114" s="19" t="inlineStr">
         <is>
           <t>ProjectPage 탭 lazy 분리 (초기 번들 ~120KB 절감)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G114" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="H114" s="19" t="n"/>
+      <c r="I114" s="19" t="inlineStr">
         <is>
           <t>ProjectPage에서 6개 탭 컴포넌트를 정적 import — 프로젝트 진입 시 전체 로드</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="J114" s="19" t="inlineStr">
         <is>
           <t>React.lazy + Suspense 적용, 활성 탭만 로드</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="K114" s="19" t="inlineStr">
         <is>
           <t>프로젝트 페이지 초기 로딩</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="L114" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="45" customHeight="1">
+      <c r="A115" s="19" t="inlineStr">
         <is>
           <t>ENH-035</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="19" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="20" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
       </c>
-      <c r="D115" s="18" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E115" t="inlineStr">
+      <c r="D115" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E115" s="19" t="inlineStr">
         <is>
           <t>번들 chunk 세분화 (index 638KB → 356KB)</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="19" t="inlineStr">
         <is>
           <t>1.1.0.0</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G115" s="19" t="inlineStr">
         <is>
           <t>1.1.0.1</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="H115" s="19" t="n"/>
+      <c r="I115" s="19" t="inlineStr">
         <is>
           <t>vite manualChunks가 vendor/grid 2개만 분리, index 638KB</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="J115" s="19" t="inlineStr">
         <is>
           <t>charts/i18n/utils chunk 추가 분리, chunkSizeWarningLimit 설정</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="K115" s="19" t="inlineStr">
         <is>
           <t>프론트엔드 빌드/초기 로딩</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="L115" s="19" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7406,6 +7406,354 @@
         </is>
       </c>
       <c r="L115" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="19" t="inlineStr">
+        <is>
+          <t>ENH-036</t>
+        </is>
+      </c>
+      <c r="B116" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D116" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E116" s="19" t="inlineStr">
+        <is>
+          <t>엑셀 Export 시트 분리 옵션 (split_sheets)</t>
+        </is>
+      </c>
+      <c r="F116" s="19" t="inlineStr">
+        <is>
+          <t>1.1.0.1</t>
+        </is>
+      </c>
+      <c r="G116" s="19" t="inlineStr">
+        <is>
+          <t>1.2.0.0</t>
+        </is>
+      </c>
+      <c r="H116" s="19" t="n"/>
+      <c r="I116" s="19" t="inlineStr">
+        <is>
+          <t>Export 시 모든 TC가 단일 시트에 출력됨, sheet_name별 분리 필요</t>
+        </is>
+      </c>
+      <c r="J116" s="19" t="inlineStr">
+        <is>
+          <t>split_sheets=true 파라미터 추가, sheet_name 기준 엑셀 탭 분리 생성 + 시트명 특수문자 치환</t>
+        </is>
+      </c>
+      <c r="K116" s="19" t="inlineStr">
+        <is>
+          <t>TC Export</t>
+        </is>
+      </c>
+      <c r="L116" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>ENH-037</t>
+        </is>
+      </c>
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C117" s="20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D117" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E117" s="19" t="inlineStr">
+        <is>
+          <t>issue_link/assignee 미사용 컬럼 제거</t>
+        </is>
+      </c>
+      <c r="F117" s="19" t="inlineStr">
+        <is>
+          <t>1.1.0.1</t>
+        </is>
+      </c>
+      <c r="G117" s="19" t="inlineStr">
+        <is>
+          <t>1.2.0.0</t>
+        </is>
+      </c>
+      <c r="H117" s="19" t="n"/>
+      <c r="I117" s="19" t="inlineStr">
+        <is>
+          <t>TestCase 모델에 issue_link, assignee 컬럼이 있으나 실제 사용하지 않음</t>
+        </is>
+      </c>
+      <c r="J117" s="19" t="inlineStr">
+        <is>
+          <t>모델/스키마에서 컬럼 삭제, 임포트 매핑(Excel/CSV/MD/Jira) _skip 처리, 그리드 컬럼 제거</t>
+        </is>
+      </c>
+      <c r="K117" s="19" t="inlineStr">
+        <is>
+          <t>TC 모델/임포트/익스포트/그리드</t>
+        </is>
+      </c>
+      <c r="L117" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="19" t="inlineStr">
+        <is>
+          <t>ENH-038</t>
+        </is>
+      </c>
+      <c r="B118" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D118" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E118" s="19" t="inlineStr">
+        <is>
+          <t>Excel Export 옵션 모달 UI</t>
+        </is>
+      </c>
+      <c r="F118" s="19" t="inlineStr">
+        <is>
+          <t>1.1.0.1</t>
+        </is>
+      </c>
+      <c r="G118" s="19" t="inlineStr">
+        <is>
+          <t>1.2.0.0</t>
+        </is>
+      </c>
+      <c r="H118" s="19" t="n"/>
+      <c r="I118" s="19" t="inlineStr">
+        <is>
+          <t>Export 버튼 클릭 시 바로 다운로드됨, 시트 분리 옵션 선택 불가</t>
+        </is>
+      </c>
+      <c r="J118" s="19" t="inlineStr">
+        <is>
+          <t>Export 버튼 → 모달 팝업 (통합/분리 라디오 선택 → 다운로드)</t>
+        </is>
+      </c>
+      <c r="K118" s="19" t="inlineStr">
+        <is>
+          <t>TC Export UI</t>
+        </is>
+      </c>
+      <c r="L118" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="19" t="inlineStr">
+        <is>
+          <t>ENH-039</t>
+        </is>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C119" s="20" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D119" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="inlineStr">
+        <is>
+          <t>프로젝트 설정 — 이름/설명 편집 기능</t>
+        </is>
+      </c>
+      <c r="F119" s="19" t="inlineStr">
+        <is>
+          <t>1.1.0.1</t>
+        </is>
+      </c>
+      <c r="G119" s="19" t="inlineStr">
+        <is>
+          <t>1.2.0.0</t>
+        </is>
+      </c>
+      <c r="H119" s="19" t="n"/>
+      <c r="I119" s="19" t="inlineStr">
+        <is>
+          <t>프로젝트 생성 후 이름/설명 수정 불가</t>
+        </is>
+      </c>
+      <c r="J119" s="19" t="inlineStr">
+        <is>
+          <t>ProjectSettings에 이름/설명 input + 저장 버튼 추가 (admin 전용)</t>
+        </is>
+      </c>
+      <c r="K119" s="19" t="inlineStr">
+        <is>
+          <t>프로젝트 설정</t>
+        </is>
+      </c>
+      <c r="L119" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="19" t="inlineStr">
+        <is>
+          <t>ENH-040</t>
+        </is>
+      </c>
+      <c r="B120" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D120" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E120" s="19" t="inlineStr">
+        <is>
+          <t>TestRunManager result 컬럼 select 위젯 전환</t>
+        </is>
+      </c>
+      <c r="F120" s="19" t="inlineStr">
+        <is>
+          <t>1.1.0.1</t>
+        </is>
+      </c>
+      <c r="G120" s="19" t="inlineStr">
+        <is>
+          <t>1.2.0.0</t>
+        </is>
+      </c>
+      <c r="H120" s="19" t="n"/>
+      <c r="I120" s="19" t="inlineStr">
+        <is>
+          <t>result 셀이 AG Grid 셀 에디터 방식 — 더블클릭 필요, 직관성 떨어짐</t>
+        </is>
+      </c>
+      <c r="J120" s="19" t="inlineStr">
+        <is>
+          <t>editable:false + 네이티브 &lt;select&gt; cellRenderer로 변경, Shift+클릭 채우기 로직 개선</t>
+        </is>
+      </c>
+      <c r="K120" s="19" t="inlineStr">
+        <is>
+          <t>TestRun 결과 입력</t>
+        </is>
+      </c>
+      <c r="L120" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>ENH-041</t>
+        </is>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C121" s="20" t="inlineStr">
+        <is>
+          <t>Trivial</t>
+        </is>
+      </c>
+      <c r="D121" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E121" s="19" t="inlineStr">
+        <is>
+          <t>test_steps/expected_result 컬럼 flex 레이아웃</t>
+        </is>
+      </c>
+      <c r="F121" s="19" t="inlineStr">
+        <is>
+          <t>1.1.0.1</t>
+        </is>
+      </c>
+      <c r="G121" s="19" t="inlineStr">
+        <is>
+          <t>1.2.0.0</t>
+        </is>
+      </c>
+      <c r="H121" s="19" t="n"/>
+      <c r="I121" s="19" t="inlineStr">
+        <is>
+          <t>고정 width로 화면 크기에 따라 빈 공간 발생</t>
+        </is>
+      </c>
+      <c r="J121" s="19" t="inlineStr">
+        <is>
+          <t>minWidth + flex:2 적용, 화면 크기에 맞게 자동 확장</t>
+        </is>
+      </c>
+      <c r="K121" s="19" t="inlineStr">
+        <is>
+          <t>TC 그리드/TestRun 그리드</t>
+        </is>
+      </c>
+      <c r="L121" s="19" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7754,6 +7754,382 @@
         </is>
       </c>
       <c r="L121" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="19" t="inlineStr">
+        <is>
+          <t>BUG-068</t>
+        </is>
+      </c>
+      <c r="B122" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D122" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E122" s="19" t="inlineStr">
+        <is>
+          <t>런 생성 이후 추가된 TC가 테스트 수행 화면에 나타나지 않음</t>
+        </is>
+      </c>
+      <c r="F122" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.1.0</t>
+        </is>
+      </c>
+      <c r="G122" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="H122" s="19" t="inlineStr">
+        <is>
+          <t>테스트 런이 이미 생성되어 있을 것</t>
+        </is>
+      </c>
+      <c r="I122" s="19" t="inlineStr">
+        <is>
+          <t>1. 프로젝트에 테스트 수행(런)을 만든다
+2. 런 생성 후 새 시트를 만들고 TC를 추가한다
+3. 테스트 수행 화면에서 해당 시트 탭을 클릭한다
+4. 배지에는 TC 개수가 표시되지만 그리드는 비어 있다</t>
+        </is>
+      </c>
+      <c r="J122" s="19" t="inlineStr">
+        <is>
+          <t>결과 행(test_results)이 런 생성 시점에만 일괄 생성되고, 이후 추가된 TC에 대해서는 생성되지 않았다. 진행 중인 런은 누락 TC의 결과 행(NS)을 자동 흡수하도록 services/run_sync_service.py 를 추가하고, TC가 생기는 모든 경로(생성/복원/복제/일괄복제/엑셀·CSV·마크다운 임포트)와 런 상세 조회, reopen 시점에 동기화를 연결했다. 완료된 런은 과거 기록 무결성을 위해 스냅샷을 유지한다.</t>
+        </is>
+      </c>
+      <c r="K122" s="19" t="inlineStr">
+        <is>
+          <t>테스트 수행 그리드, 대시보드 집계, 리포트, 엑셀 내보내기</t>
+        </is>
+      </c>
+      <c r="L122" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="19" t="inlineStr">
+        <is>
+          <t>BUG-069</t>
+        </is>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C123" s="20" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D123" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E123" s="19" t="inlineStr">
+        <is>
+          <t>결과 0건 시트 선택 시 시트 탭 바가 사라져 되돌아갈 수 없음</t>
+        </is>
+      </c>
+      <c r="F123" s="19" t="inlineStr">
+        <is>
+          <t>FE 1.2.1.0</t>
+        </is>
+      </c>
+      <c r="G123" s="19" t="inlineStr">
+        <is>
+          <t>FE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="H123" s="19" t="inlineStr">
+        <is>
+          <t>결과가 0건인 시트가 존재할 것</t>
+        </is>
+      </c>
+      <c r="I123" s="19" t="inlineStr">
+        <is>
+          <t>1. 테스트 수행 화면에서 런을 선택한다
+2. 결과가 0건인 시트 탭을 클릭한다
+3. 그리드가 비면서 하단 시트 탭 바가 통째로 사라진다
+4. 다른 시트나 전체로 돌아갈 방법이 없다 (새로고침 필요)</t>
+        </is>
+      </c>
+      <c r="J123" s="19" t="inlineStr">
+        <is>
+          <t>시트 탭 바 렌더 조건에 results.length &gt; 0 이 포함되어, 결과 0건 시트를 선택하면 탭 바 자체가 언마운트됐다. 해당 조건을 제거해 런이 선택되어 있으면 항상 탭 바를 유지하도록 수정했다.</t>
+        </is>
+      </c>
+      <c r="K123" s="19" t="inlineStr">
+        <is>
+          <t>테스트 수행 화면 시트 탭</t>
+        </is>
+      </c>
+      <c r="L123" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="19" t="inlineStr">
+        <is>
+          <t>BUG-070</t>
+        </is>
+      </c>
+      <c r="B124" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D124" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>시트 탭 배지 숫자가 그리드 행 수와 불일치</t>
+        </is>
+      </c>
+      <c r="F124" s="19" t="inlineStr">
+        <is>
+          <t>FE 1.2.1.0</t>
+        </is>
+      </c>
+      <c r="G124" s="19" t="inlineStr">
+        <is>
+          <t>FE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="H124" s="19" t="n"/>
+      <c r="I124" s="19" t="inlineStr">
+        <is>
+          <t>1. 완료된 런을 연다
+2. 런 완료 후 추가된 TC가 있는 시트 탭을 본다
+3. 배지에는 TC 라이브러리 기준 개수가 나오지만 그리드 행 수는 다르다</t>
+        </is>
+      </c>
+      <c r="J124" s="19" t="inlineStr">
+        <is>
+          <t>배지는 시트 API 의 tc_count(TC 라이브러리 기준), 그리드는 런 스냅샷 기준이라 기준이 서로 달랐다. 배지를 해당 런의 결과 수로 계산하도록 변경해, 진행 중/완료 런 모두 배지와 그리드 행 수가 항상 일치한다.</t>
+        </is>
+      </c>
+      <c r="K124" s="19" t="inlineStr">
+        <is>
+          <t>테스트 수행 화면 시트 탭 배지</t>
+        </is>
+      </c>
+      <c r="L124" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
+          <t>BUG-071</t>
+        </is>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C125" s="20" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D125" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t>런에 나중에 편입된 TC가 번호 순서를 벗어나 맨 뒤에 표시</t>
+        </is>
+      </c>
+      <c r="F125" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.1.0</t>
+        </is>
+      </c>
+      <c r="G125" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="H125" s="19" t="inlineStr">
+        <is>
+          <t>런 생성 이후 기존 TC 사이에 끼는 번호로 TC 를 추가할 것</t>
+        </is>
+      </c>
+      <c r="I125" s="19" t="inlineStr">
+        <is>
+          <t>1. TC 번호 1, 3 을 만들고 런을 생성한다
+2. 런 생성 후 번호 2 로 TC 를 추가한다
+3. 런 상세를 조회하면 번호가 1, 3, 2 순으로 반환된다</t>
+        </is>
+      </c>
+      <c r="J125" s="19" t="inlineStr">
+        <is>
+          <t>결과 행이 런에 편입된 순서로 저장되는데 조회 시 정렬이 없었다. 런 상세 API 와 리포트 엑셀, 프론트 그리드 세 곳에서 TC 번호 순 정렬을 보장하도록 수정했다.</t>
+        </is>
+      </c>
+      <c r="K125" s="19" t="inlineStr">
+        <is>
+          <t>테스트 수행 그리드, 리포트 엑셀</t>
+        </is>
+      </c>
+      <c r="L125" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="19" t="inlineStr">
+        <is>
+          <t>SEC-013</t>
+        </is>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D126" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E126" s="19" t="inlineStr">
+        <is>
+          <t>viewer 권한 조회만으로 DB 쓰기가 발생</t>
+        </is>
+      </c>
+      <c r="F126" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="G126" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="H126" s="19" t="inlineStr">
+        <is>
+          <t>공개 프로젝트일 것</t>
+        </is>
+      </c>
+      <c r="I126" s="19" t="inlineStr">
+        <is>
+          <t>1. 프로젝트 멤버가 아닌 사용자가 공개 프로젝트의 런을 조회한다
+2. 누락 TC 보정 로직이 동작해 test_results 에 INSERT 가 발생한다</t>
+        </is>
+      </c>
+      <c r="J126" s="19" t="inlineStr">
+        <is>
+          <t>런 누락 TC 보정을 런 상세 조회(GET)에 넣으면서, 읽기 전용으로 문서화된 viewer 역할이 조회만으로 쓰기를 유발했다. 공개 프로젝트는 비멤버도 viewer 로 취급되므로 노출 범위가 넓었다. 보정을 tester 이상에서만 수행하도록 제한했다.</t>
+        </is>
+      </c>
+      <c r="K126" s="19" t="inlineStr">
+        <is>
+          <t>런 상세 조회 API 권한</t>
+        </is>
+      </c>
+      <c r="L126" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>BUG-072</t>
+        </is>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="C127" s="20" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D127" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
+          <t>SQLite busy_timeout 미설정으로 동시 쓰기 시 즉시 실패 가능</t>
+        </is>
+      </c>
+      <c r="F127" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.1.0</t>
+        </is>
+      </c>
+      <c r="G127" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="H127" s="19" t="n"/>
+      <c r="I127" s="19" t="inlineStr">
+        <is>
+          <t>1. 다중 요청이 동시에 쓰기를 시도한다
+2. 잠금 경합 시 대기 없이 database is locked 로 즉시 실패한다</t>
+        </is>
+      </c>
+      <c r="J127" s="19" t="inlineStr">
+        <is>
+          <t>database.py 에 journal_mode=WAL 은 있었으나 busy_timeout 이 없어 경합 시 대기하지 않고 즉시 실패했다. PRAGMA busy_timeout=30000 을 추가했다. 이번 변경으로 결과 행 삽입 경로가 늘어 경합 노출이 커진 점도 고려했다.</t>
+        </is>
+      </c>
+      <c r="K127" s="19" t="inlineStr">
+        <is>
+          <t>DB 쓰기 전반</t>
+        </is>
+      </c>
+      <c r="L127" s="19" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8130,6 +8130,64 @@
         </is>
       </c>
       <c r="L127" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="19" t="inlineStr">
+        <is>
+          <t>ENH-042</t>
+        </is>
+      </c>
+      <c r="B128" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>Trivial</t>
+        </is>
+      </c>
+      <c r="D128" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E128" s="19" t="inlineStr">
+        <is>
+          <t>엠대시/엔대시를 일반 하이픈으로 전면 교체</t>
+        </is>
+      </c>
+      <c r="F128" s="19" t="inlineStr">
+        <is>
+          <t>FE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="G128" s="19" t="inlineStr">
+        <is>
+          <t>FE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="H128" s="19" t="n"/>
+      <c r="I128" s="19" t="inlineStr">
+        <is>
+          <t>레포 전역의 엠대시(U+2014)와 엔대시(U+2013) 198건을 일반 하이픈으로 교체했다. 릴리즈 노트 95건 + 나머지 26개 파일 103건.</t>
+        </is>
+      </c>
+      <c r="J128" s="19" t="inlineStr">
+        <is>
+          <t>전역 개발 규칙에서 엠대시 사용을 금지하고 있으나 과거 작성분에 잔존했다. 대상은 주석, 로그 문자열, 문서, UI 표시 문구이며 로직 비교에 쓰이는 곳은 없었다. i18n 문구 변경은 설정/매뉴얼 페이지 렌더링을 캡처해 확인했다.</t>
+        </is>
+      </c>
+      <c r="K128" s="19" t="inlineStr">
+        <is>
+          <t>문서, 코드 주석, 설정/매뉴얼 페이지 표시 문구</t>
+        </is>
+      </c>
+      <c r="L128" s="19" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8188,6 +8188,202 @@
         </is>
       </c>
       <c r="L128" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="19" t="inlineStr">
+        <is>
+          <t>BUG-073</t>
+        </is>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C129" s="20" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
+          <t>backend/.env 가 전혀 로드되지 않아 재시작마다 로그인 세션이 끊김</t>
+        </is>
+      </c>
+      <c r="F129" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="G129" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.3.0</t>
+        </is>
+      </c>
+      <c r="H129" s="19" t="inlineStr">
+        <is>
+          <t>신규 clone 후 README 3단계대로 backend/.env 를 만들고 SECRET_KEY 를 임의 값으로 변경한 상태</t>
+        </is>
+      </c>
+      <c r="I129" s="19" t="inlineStr">
+        <is>
+          <t>1. git clone 후 cp backend/.env.example backend/.env
+2. .env 의 SECRET_KEY 를 임의 문자열로 변경
+3. cd backend &amp;&amp; uvicorn main:app --port 8008 로 기동
+4. 기동 로그에 'SECRET_KEY not set - using random key (dev only)' 가 출력됨
+5. 로그인 후 서버를 재시작하고 같은 쿠키로 GET /api/auth/me 호출
+6. 401 Unauthorized 반환</t>
+        </is>
+      </c>
+      <c r="J129" s="19" t="inlineStr">
+        <is>
+          <t>레포 어디에도 .env 를 읽는 코드가 없었다. load_dotenv() 호출 0건이고 run_dev.bat, run_dev.sh, playwright.config.ts, CI 어느 것도 --env-file 을 주지 않아 auth.py 의 os.getenv('SECRET_KEY','') 가 항상 빈 값을 받았다. 그 결과 기동마다 랜덤 키가 생성돼 재시작 시 모든 토큰이 무효화됐다. backend/env_setup.py 를 신설해 auth.py, database.py, main.py, alembic/env.py 최상단에서 임포트하도록 했다. override=False 라 실제 환경변수와 conftest 가 지정하는 DATABASE_URL 이 .env 보다 우선하므로 테스트 격리는 유지된다. 회귀 테스트 backend/test_env_loading.py 5건 추가.</t>
+        </is>
+      </c>
+      <c r="K129" s="19" t="inlineStr">
+        <is>
+          <t>로그인 세션 유지, SECRET_KEY / ENV / CORS_ORIGINS / TOKEN_EXPIRE_HOURS / DATABASE_URL 등 모든 환경설정. ENV=production 지정이 동작하지 않던 문제 포함</t>
+        </is>
+      </c>
+      <c r="L129" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="19" t="inlineStr">
+        <is>
+          <t>BUG-074</t>
+        </is>
+      </c>
+      <c r="B130" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D130" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="inlineStr">
+        <is>
+          <t>Python 3.14 에서 백엔드 의존성 설치가 전체 실패</t>
+        </is>
+      </c>
+      <c r="F130" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="G130" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.3.0</t>
+        </is>
+      </c>
+      <c r="H130" s="19" t="inlineStr">
+        <is>
+          <t>Python 3.14 환경(3.14.6 에서 확인)</t>
+        </is>
+      </c>
+      <c r="I130" s="19" t="inlineStr">
+        <is>
+          <t>1. Python 3.14 로 가상환경 생성
+2. pip install -r backend/requirements.txt
+3. pydantic-core 단계에서 'Rust not found, installing into a temporary directory' 후 'maturin failed'
+4. 'error: metadata-generation-failed' 로 설치 중단
+5. fastapi, uvicorn 등 나머지 패키지도 설치되지 않아 백엔드 기동 불가</t>
+        </is>
+      </c>
+      <c r="J130" s="19" t="inlineStr">
+        <is>
+          <t>pydantic[email]==2.11.7 이 pydantic-core==2.33.2 를 정확히 고정하는데, 2.33.2 는 휠 98개를 배포하면서 cp314 휠을 하나도 내지 않았다. 그래서 pip 이 소스 빌드로 폴백하고 pydantic-core 는 Rust 로 작성돼 cargo 가 필요하다. pydantic-core 가 cp314 휠을 처음 낸 버전은 2.35.0 이다. pydantic[email]==2.13.4 (pydantic-core 2.46.4) 로 상향해 해결했다. 나머지 바이너리 의존성은 전부 cp314 휠이 있어 pydantic 단독 원인이었다. 재발 방지로 CI 에 Python 3.12/3.14 설치 검증 매트릭스를 추가하고 pip install --only-binary=:all: 로 소스 빌드 폴백을 금지했다. GitHub 러너에는 Rust 가 있어 일반 설치로는 이 사고를 잡지 못하기 때문이다.</t>
+        </is>
+      </c>
+      <c r="K130" s="19" t="inlineStr">
+        <is>
+          <t>신규 clone 사용자의 백엔드 설치 전체. Python 3.14 사용자는 서버를 아예 띄울 수 없었다</t>
+        </is>
+      </c>
+      <c r="L130" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="19" t="inlineStr">
+        <is>
+          <t>BUG-075</t>
+        </is>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C131" s="20" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D131" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t>README 의 백엔드 테스트 절차가 의존성 누락으로 즉시 실패</t>
+        </is>
+      </c>
+      <c r="F131" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.2.0</t>
+        </is>
+      </c>
+      <c r="G131" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.3.0</t>
+        </is>
+      </c>
+      <c r="H131" s="19" t="inlineStr">
+        <is>
+          <t>신규 clone 후 pip install -r backend/requirements.txt 만 수행한 상태</t>
+        </is>
+      </c>
+      <c r="I131" s="19" t="inlineStr">
+        <is>
+          <t>1. cd backend &amp;&amp; python -m pytest -v
+2. 'No module named pytest' 로 실패</t>
+        </is>
+      </c>
+      <c r="J131" s="19" t="inlineStr">
+        <is>
+          <t>pytest 와 requests(conftest.py 가 임포트한다)가 어느 requirements 파일에도 없었다. .github/workflows/ci.yml 만 pip install -r requirements.txt pytest requests 로 인라인으로 채워 CI 만 통과하고 있었다. backend/requirements-dev.txt 를 신설하고 CI 도 이를 사용하도록 바꿨다. 아울러 CI 가 pytest test_security.py 로 파일을 명시해 pytest.ini 의 testpaths 가 무시되던 문제(파일 지정 169건 대 무인자 173건)를 무인자 실행으로 바로잡아 신규 회귀 테스트가 게이트에 포함되게 했다. README 와 CONTRIBUTING 에 테스트 의존성 설치와 npx playwright install chromium 안내를 추가하고, Python 지원 범위 표기(3.11+ 대 3.12)를 3.11 ~ 3.14 로 통일했다.</t>
+        </is>
+      </c>
+      <c r="K131" s="19" t="inlineStr">
+        <is>
+          <t>테스트 실행 절차, CI 게이트 범위, 설치 문서</t>
+        </is>
+      </c>
+      <c r="L131" s="19" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8384,6 +8384,64 @@
         </is>
       </c>
       <c r="L131" s="19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="19" t="inlineStr">
+        <is>
+          <t>ENH-043</t>
+        </is>
+      </c>
+      <c r="B132" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="D132" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E132" s="19" t="inlineStr">
+        <is>
+          <t>계정 복구 (아이디 찾기 / 비밀번호 재설정) 추가</t>
+        </is>
+      </c>
+      <c r="F132" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.2.3.0</t>
+        </is>
+      </c>
+      <c r="G132" s="19" t="inlineStr">
+        <is>
+          <t>BE 1.3.0.0</t>
+        </is>
+      </c>
+      <c r="H132" s="19" t="n"/>
+      <c r="I132" s="19" t="inlineStr">
+        <is>
+          <t>관리자 승인 기반 계정 복구 요청 큐를 신설했다. account_requests 테이블과 마이그레이션(05f8800a57f5, 06933fddb519에서 체이닝)을 추가하고, 공개 요청 접수 / 코드로 비밀번호 재설정과 관리자 목록 / 승인 / 반려까지 5개 엔드포인트를 구현했다. 아이디 찾기 승인은 아이디를, 비밀번호 재설정 승인은 12자리(secrets.token_urlsafe(9)) 1회용 코드를 발급하며, 코드는 bcrypt 해시로만 저장하고 24시간 후 만료된다. 로그인 화면에 '계정 도움 요청' 링크와 /account-help, /reset-password 페이지, 관리자 페이지의 계정 복구 요청 큐 UI를 추가했다.</t>
+        </is>
+      </c>
+      <c r="J132" s="19" t="inlineStr">
+        <is>
+          <t>여러 사용자가 쓰기 시작하면서 아이디나 비밀번호를 잊은 사용자가 스스로 복구할 경로가 없었다. User 모델에 연락 수단이 없고 SMTP 설정도 없어 메일 기반 셀프 서비스가 불가능해 관리자 승인 큐 방식을 택했다. 계정 열거를 막기 위해 접수 응답은 계정 존재 여부와 무관하게 동일한 201과 동일한 본문을 반환하도록 실서버에서 검증했고, 코드 대입 4가지 실패 모드도 동일한 401을 반환한다. 사용한 코드는 같은 커밋에서 completed 로 바뀌고 code_hash 가 즉시 지워진다. 부수적으로 401 응답 인터셉터가 /account-help, /reset-password, (기존부터) /register 를 전부 로그인 화면으로 리다이렉트해 직접 URL 접근이 불가능했고 재설정 화면의 코드 오류 메시지까지 삼키던 문제를 4개 공개 경로 화이트리스트로 함께 고쳤다. backend/test_account_requests.py 20건 신규, 프론트엔드 테스트는 381건에서 386건으로 늘었다.</t>
+        </is>
+      </c>
+      <c r="K132" s="19" t="inlineStr">
+        <is>
+          <t>로그인 화면, /account-help, /reset-password 페이지, 관리자 페이지 계정 복구 요청 큐, 인증 API 401 처리</t>
+        </is>
+      </c>
+      <c r="L132" s="19" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U137"/>
+  <dimension ref="A1:U136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -606,6 +606,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -660,6 +663,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -714,6 +720,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -767,6 +776,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -820,6 +832,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -872,6 +887,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -927,6 +945,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -979,6 +1000,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1044,6 +1068,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1108,6 +1135,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U11" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1171,6 +1201,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U12" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1233,6 +1266,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U13" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1296,6 +1332,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1359,6 +1398,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U15" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1421,6 +1463,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U16" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1486,6 +1531,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U17" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1549,6 +1597,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U18" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1612,6 +1663,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U19" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1656,8 +1710,11 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미해결</t>
-        </is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -1706,6 +1763,11 @@
           <t>미해결</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SYM-6</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1763,6 +1825,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U22" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1820,6 +1885,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U23" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1877,6 +1945,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U24" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1930,6 +2001,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U25" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1983,6 +2057,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U26" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2036,6 +2113,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U27" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2089,6 +2169,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U28" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2142,6 +2225,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U29" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2195,6 +2281,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U30" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2248,6 +2337,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U31" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2301,6 +2393,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U32" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2364,6 +2459,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U33" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2427,6 +2525,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U34" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2490,6 +2591,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U35" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2553,6 +2657,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U36" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2610,6 +2717,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U37" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2667,6 +2777,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U38" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2724,6 +2837,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U39" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2780,6 +2896,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U40" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -2835,6 +2954,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U41" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2898,6 +3020,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U42" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2961,6 +3086,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U43" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3024,6 +3152,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U44" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3086,6 +3217,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U45" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="46">
@@ -3141,6 +3275,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U46" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3203,6 +3340,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U47" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="48">
@@ -3258,6 +3398,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U48" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3321,6 +3464,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U49" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3384,6 +3530,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U50" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3447,6 +3596,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U51" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3510,6 +3662,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U52" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3573,6 +3728,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U53" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3636,6 +3794,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U54" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3699,6 +3860,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U55" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3762,6 +3926,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U56" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3825,6 +3992,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U57" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3888,6 +4058,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U58" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3951,6 +4124,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U59" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4014,6 +4190,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U60" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4077,6 +4256,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U61" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4134,6 +4316,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U62" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4191,6 +4376,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U63" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4248,6 +4436,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U64" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4305,6 +4496,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U65" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4362,6 +4556,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U66" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4415,6 +4612,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U67" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4478,6 +4678,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U68" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4541,6 +4744,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U69" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4604,6 +4810,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U70" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4667,6 +4876,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U71" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4730,6 +4942,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U72" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4793,6 +5008,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U73" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4849,6 +5067,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U74" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="75">
@@ -4904,6 +5125,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U75" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4961,6 +5185,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U76" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5010,8 +5237,11 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>미해결</t>
-        </is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="78">
@@ -5070,6 +5300,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U78" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5133,6 +5366,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U79" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5195,6 +5431,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U80" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5258,6 +5497,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U81" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5321,6 +5563,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U82" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5384,6 +5629,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U83" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5447,6 +5695,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U84" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5510,6 +5761,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U85" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5573,6 +5827,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U86" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5630,6 +5887,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U87" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5687,6 +5947,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U88" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5744,6 +6007,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U89" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5801,6 +6067,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U90" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5858,6 +6127,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U91" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5915,6 +6187,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U92" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5972,6 +6247,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U93" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6029,6 +6307,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U94" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6086,6 +6367,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U95" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6143,6 +6427,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U96" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6200,6 +6487,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U97" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6257,6 +6547,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U98" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6314,6 +6607,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U99" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6371,6 +6667,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U100" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6428,6 +6727,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U101" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6485,6 +6787,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U102" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6542,6 +6847,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U103" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6599,6 +6907,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U104" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6656,6 +6967,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U105" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7283,6 +7597,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U116" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7340,6 +7657,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U117" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7397,6 +7717,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U118" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7454,6 +7777,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U119" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7511,6 +7837,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U120" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7567,6 +7896,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U121" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="122">
@@ -7633,6 +7965,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U122" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7698,6 +8033,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U123" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7757,6 +8095,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U124" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7821,6 +8162,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U125" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7884,6 +8228,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U126" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7942,6 +8289,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U127" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7998,6 +8348,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U128" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="129">
@@ -8066,6 +8419,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U129" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8132,6 +8488,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U130" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8195,6 +8554,9 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U131" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8251,6 +8613,9 @@
         <is>
           <t>완료</t>
         </is>
+      </c>
+      <c r="U132" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="133">
@@ -8630,68 +8995,6 @@
       <c r="U136" t="inlineStr">
         <is>
           <t>SYM-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>ENH-046</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>db</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>[ENH-002] PostgreSQL 전환 준비</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>SQLite 로 운영한다</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>PostgreSQL 로 옮길 수 있는 상태가 된다</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>SQLite 동시성 한계, 프로덕션 환경 대비</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>0.3.0.0</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SYM-6</t>
         </is>
       </c>
     </row>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -564,6 +564,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Major</t>
@@ -621,6 +626,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -678,6 +688,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Major</t>
@@ -735,6 +750,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Major</t>
@@ -791,6 +811,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Major</t>
@@ -847,6 +872,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -901,6 +931,11 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bug</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -960,6 +995,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Major</t>
@@ -1014,6 +1054,11 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bug</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1083,6 +1128,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Major</t>
@@ -1150,6 +1200,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -1216,6 +1271,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Major</t>
@@ -1281,6 +1341,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Major</t>
@@ -1347,6 +1412,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -1413,6 +1483,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Major</t>
@@ -1477,6 +1552,11 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bug</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1546,6 +1626,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -1612,6 +1697,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -1678,6 +1768,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>Major</t>
@@ -1728,6 +1823,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Major</t>
@@ -1780,6 +1880,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Major</t>
@@ -1840,6 +1945,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -1900,6 +2010,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -1960,6 +2075,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>Major</t>
@@ -2016,6 +2136,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>Major</t>
@@ -2072,6 +2197,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>Major</t>
@@ -2128,6 +2258,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -2184,6 +2319,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -2240,6 +2380,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -2296,6 +2441,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>Major</t>
@@ -2352,6 +2502,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -2408,6 +2563,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -2474,6 +2634,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -2540,6 +2705,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -2606,6 +2776,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>Major</t>
@@ -2672,6 +2847,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>Major</t>
@@ -2732,6 +2912,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>Major</t>
@@ -2792,6 +2977,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -2852,6 +3042,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -2910,6 +3105,11 @@
       <c r="B41" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bug</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2969,6 +3169,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -3035,6 +3240,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -3101,6 +3311,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>Major</t>
@@ -3167,6 +3382,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>Major</t>
@@ -3231,6 +3451,11 @@
       <c r="B46" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bug</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3290,6 +3515,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>Major</t>
@@ -3354,6 +3584,11 @@
       <c r="B48" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>bug</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3413,6 +3648,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>Major</t>
@@ -3479,6 +3719,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>Major</t>
@@ -3545,6 +3790,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -3611,6 +3861,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -3677,6 +3932,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -3743,6 +4003,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -3809,6 +4074,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -3875,6 +4145,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>Major</t>
@@ -3941,6 +4216,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>Major</t>
@@ -4007,6 +4287,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -4073,6 +4358,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>Major</t>
@@ -4139,6 +4429,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>Major</t>
@@ -4205,6 +4500,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -4271,6 +4571,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>Major</t>
@@ -4331,6 +4636,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>Major</t>
@@ -4391,6 +4701,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>Major</t>
@@ -4451,6 +4766,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -4511,6 +4831,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>Major</t>
@@ -4571,6 +4896,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -4627,6 +4957,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>Major</t>
@@ -4693,6 +5028,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -4759,6 +5099,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -4825,6 +5170,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -4891,6 +5241,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -4957,6 +5312,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -5023,6 +5383,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -5081,6 +5446,11 @@
       <c r="B75" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>bug</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5140,6 +5510,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -5200,6 +5575,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -5255,6 +5635,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -5315,6 +5700,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -5381,6 +5771,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>Major</t>
@@ -5446,6 +5841,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>Major</t>
@@ -5512,6 +5912,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -5578,6 +5983,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>Major</t>
@@ -5644,6 +6054,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -5710,6 +6125,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
           <t>Major</t>
@@ -5776,6 +6196,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -5842,6 +6267,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -5902,6 +6332,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -5962,6 +6397,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -6022,6 +6462,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -6082,6 +6527,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -6142,6 +6592,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>Major</t>
@@ -6202,6 +6657,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>Major</t>
@@ -6262,6 +6722,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -6322,6 +6787,11 @@
           <t>2026-03-23</t>
         </is>
       </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -6382,6 +6852,11 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
           <t>Major</t>
@@ -6442,6 +6917,11 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -6502,6 +6982,11 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -6562,6 +7047,11 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -6622,6 +7112,11 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -6682,6 +7177,11 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -6742,6 +7242,11 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>Major</t>
@@ -6802,6 +7307,11 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -6862,6 +7372,11 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -6922,6 +7437,11 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -7552,6 +8072,11 @@
           <t>2026-04-08</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -7612,6 +8137,11 @@
           <t>2026-04-08</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -7672,6 +8202,11 @@
           <t>2026-04-08</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -7732,6 +8267,11 @@
           <t>2026-04-08</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -7792,6 +8332,11 @@
           <t>2026-04-08</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -7852,6 +8397,11 @@
           <t>2026-04-08</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -7910,6 +8460,11 @@
       <c r="B122" t="inlineStr">
         <is>
           <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>bug</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7980,6 +8535,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>Major</t>
@@ -8048,6 +8608,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -8061,6 +8626,11 @@
       <c r="F124" t="inlineStr">
         <is>
           <t>시트 탭 배지 숫자가 그리드 행 수와 불일치</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8110,6 +8680,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -8177,6 +8752,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -8243,6 +8823,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>Major</t>
@@ -8256,6 +8841,11 @@
       <c r="F127" t="inlineStr">
         <is>
           <t>SQLite busy_timeout 미설정으로 동시 쓰기 시 즉시 실패 가능</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8304,6 +8894,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -8362,6 +8957,11 @@
       <c r="B129" t="inlineStr">
         <is>
           <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>bug</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8434,6 +9034,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -8503,6 +9108,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>Major</t>
@@ -8567,6 +9177,11 @@
       <c r="B132" t="inlineStr">
         <is>
           <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>enhancement</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8970,6 +9585,11 @@
       <c r="O136" t="inlineStr">
         <is>
           <t>동작 변화 없이 경고만 사라졌다. 남은 3건은 uvicorn 내부</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>uvicorn 이 내부에서 내는 `websockets.legacy` 경고는 우리 코드가 아니라 손대지 않는다.</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -421,7 +421,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U136"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -7502,6 +7502,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -7517,6 +7522,11 @@
           <t>대시보드 SQL 집계 전환 (ORM 전체 로드 → GROUP BY)</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>dashboard summary/priority/category/assignee/rounds/heatmap가 전체 ORM 객체를 Python에서 카운팅</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>dashboard summary/priority/category/assignee/rounds/heatmap가 전체 ORM 객체를 Python에서 카운팅</t>
@@ -7545,6 +7555,11 @@
       <c r="T106" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SYM-13</t>
         </is>
       </c>
     </row>
@@ -7559,6 +7574,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -7574,6 +7594,11 @@
           <t>Overview SQL 집계 전환 (Python 카운팅 → SQL 서브쿼리)</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>overview 엔드포인트가 전체 TestResult ORM 로드 후 Python _count_results로 집계</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>overview 엔드포인트가 전체 TestResult ORM 로드 후 Python _count_results로 집계</t>
@@ -7602,6 +7627,11 @@
       <c r="T107" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SYM-14</t>
         </is>
       </c>
     </row>
@@ -7616,6 +7646,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -7631,6 +7666,11 @@
           <t>TestPlan 목록 N+1 제거 (플랜별 개별 조회 → SQL 2회)</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>list_test_plans에서 플랜마다 run_count + _plan_progress 개별 DB 조회 (N+1)</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>list_test_plans에서 플랜마다 run_count + _plan_progress 개별 DB 조회 (N+1)</t>
@@ -7659,6 +7699,11 @@
       <c r="T108" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SYM-15</t>
         </is>
       </c>
     </row>
@@ -7673,6 +7718,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -7688,6 +7738,11 @@
           <t>TestRun 생성/복제 bulk insert 적용</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>create_testrun/clone에서 TC당 개별 db.add() — 5000건 시 ~7초</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>create_testrun/clone에서 TC당 개별 db.add() — 5000건 시 ~7초</t>
@@ -7716,6 +7771,11 @@
       <c r="T109" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SYM-16</t>
         </is>
       </c>
     </row>
@@ -7730,6 +7790,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -7745,6 +7810,11 @@
           <t>결과 제출 N+1 제거 (per-item .first() → IN prefetch)</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>submit_results에서 결과마다 기존 레코드를 개별 .first()로 조회</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr">
         <is>
           <t>submit_results에서 결과마다 기존 레코드를 개별 .first()로 조회</t>
@@ -7773,6 +7843,11 @@
       <c r="T110" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SYM-17</t>
         </is>
       </c>
     </row>
@@ -7787,6 +7862,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
           <t>Minor</t>
@@ -7802,6 +7882,11 @@
           <t>리포트 SQL 집계 + 이중 로드 제거</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>report Excel에서 _build_report_data + 별도 db.query 이중 로드, summary를 Python 카운팅</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
           <t>report Excel에서 _build_report_data + 별도 db.query 이중 로드, summary를 Python 카운팅</t>
@@ -7830,6 +7915,11 @@
       <c r="T111" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SYM-18</t>
         </is>
       </c>
     </row>
@@ -7844,6 +7934,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -7859,6 +7954,11 @@
           <t>SQLite WAL 모드 활성화</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SQLite 기본 journal_mode=delete, 동시 읽기/쓰기 시 lock</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr">
         <is>
           <t>SQLite 기본 journal_mode=delete, 동시 읽기/쓰기 시 lock</t>
@@ -7887,6 +7987,11 @@
       <c r="T112" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SYM-19</t>
         </is>
       </c>
     </row>
@@ -7901,6 +8006,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -7916,6 +8026,11 @@
           <t>시트 트리 순회 N+1 제거 (_collect_descendant_names)</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>_collect_descendant_names에서 재귀 while 루프로 시트마다 개별 DB 조회</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr">
         <is>
           <t>_collect_descendant_names에서 재귀 while 루프로 시트마다 개별 DB 조회</t>
@@ -7944,6 +8059,11 @@
       <c r="T113" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SYM-20</t>
         </is>
       </c>
     </row>
@@ -7958,6 +8078,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -7973,6 +8098,11 @@
           <t>ProjectPage 탭 lazy 분리 (초기 번들 ~120KB 절감)</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ProjectPage에서 6개 탭 컴포넌트를 정적 import — 프로젝트 진입 시 전체 로드</t>
+        </is>
+      </c>
       <c r="K114" t="inlineStr">
         <is>
           <t>ProjectPage에서 6개 탭 컴포넌트를 정적 import — 프로젝트 진입 시 전체 로드</t>
@@ -8001,6 +8131,11 @@
       <c r="T114" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SYM-21</t>
         </is>
       </c>
     </row>
@@ -8015,6 +8150,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
           <t>Trivial</t>
@@ -8030,6 +8170,11 @@
           <t>번들 chunk 세분화 (index 638KB → 356KB)</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>vite manualChunks가 vendor/grid 2개만 분리, index 638KB</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
           <t>vite manualChunks가 vendor/grid 2개만 분리, index 638KB</t>
@@ -8058,6 +8203,11 @@
       <c r="T115" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SYM-22</t>
         </is>
       </c>
     </row>
@@ -9699,6 +9849,7 @@
         <v>94</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -9756,6 +9907,7 @@
         <v>18</v>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,8 +420,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U136"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:U147"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -9768,6 +9768,1214 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BUG-078</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>TC ID 가 프로젝트 안에서 중복돼 사전조건 참조가 엉뚱한 TC 를 가리킨다</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>- 한 프로젝트 안에 같은 TC ID 를 가진 TC 가 둘 이상 생긴다.
+- 사전조건 참조(`&lt;TC-ID&gt; 의 사전조건 참조`)를 푸는 색인이 프로젝트 전체 TC 로 만들어져서, 중복이 있으면 참조가 어느 쪽을 가리키는지 정해지지 않는다.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>- TC ID 는 프로젝트 안에서 유일하다.
+- 사전조건 참조는 언제 풀어도 같은 TC 를 가리킨다.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>- 내보내기의 펼친 사전조건이 참조 대상이 아닌 다른 TC 의 내용을 담는다. 데이터 손상이다.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>- 프로젝트에 사전조건 참조를 쓰는 TC 가 있다.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>1. 같은 TC ID 가 든 파일을 두 번 임포트한다.
+2. 또는 다른 시트에 같은 TC ID 로 임포트한다.
+3. 또는 TC 하나를 두 번 복제한다.
+4. 사전조건 참조를 쓰는 TC 를 엑셀로 내보낸다.
+5. 펼쳐진 사전조건 내용을 원본과 대조한다.</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>- `precondition_service.build_index` 가 프로젝트 전체 TC 로 색인을 만든다.
+- `import_service` 의 `existing_map` 은 루프 시작 전 스냅샷이라 루프 안에서 새로 만든 행을 다시 담지 않는다.
+- 같은 `existing_map` 이 시트 단위인데 유일성 요구는 프로젝트 단위다.</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>원인: 중복이 생기는 경로가 넷이었고 넷 다 막혀 있지 않았다.
+- 임포트: `existing_map` 이 루프 시작 전 스냅샷이고 시트 단위였다.
+- 복제: `tc_id` 를 `{원본}-copy` 로 고정해 두 번 복제하면 겹쳤다.
+- 복원: 지운 사이에 같은 ID 가 새로 생겼으면 겹쳤다.
+- DB: `(project_id, tc_id)` 유니크 제약이 없었다.
+수정 내용: - 세 파서 모두 프로젝트 전체 `taken` 집합을 들고 다니며 빈 번호를 찾는다.
+- 복제가 원본 ID 에서 빈 번호를 새로 찾는다.
+- 복원이 `deleted_at` 을 풀기 전에 `taken` 을 조회한다(autoflush 때문에 순서가 중요하다).
+- 마이그레이션 `b7d3c9a1e450`: `(project_id, tc_id)` 부분 유니크 인덱스. `deleted_at IS NULL` 조건이 없으면 지운 TC 가 ID 를 계속 물어 같은 번호를 다시 못 쓴다.
+- 마이그레이션이 인덱스를 걸기 전에 중복을 스스로 정리한다. 가장 먼저 만든 행이 원래 ID 를 지키고 나머지에 `-2`, `-3` 을 붙이며 바꾼 내역을 WARNING 으로 남긴다. 앱 기동 시 자동 실행되므로(main.py lifespan) 여기서 실패하면 앱이 아예 뜨지 않는다.
+- 중복 시도가 500 이 아니라 409 와 안내 문구를 받게 IntegrityError 핸들러를 붙였다.
+- `services/tc_id_service.py` 신설.</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>- DB 부분 유니크 인덱스로 네 경로를 한 자리에서 막는다.
+- `backend/tests_unit/` 신설. `test_tc_id_dedup.py`, `test_unique_tc_id_migration.py`.
+- `backend/conftest.py` 의 `_server` 픽스처는 8008 에 서버가 떠 있으면 그 서버를 쓰고 admin 을 시드해서, 개발 서버를 켠 채로 pytest 를 돌리면 실 DB 에 쓰기가 들어간다. 같은 이름 픽스처를 no-op 으로 덮어 그 경로를 막았고 각 테스트는 임시 DB 만 쓴다.</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>- TC 임포트, 복제, 복원, 사전조건 참조 해석, 엑셀 내보내기.
+- 기존 DB 에 중복이 있으면 첫 기동 때 ID 가 `-2`, `-3` 으로 바뀐다.</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>BE 1.3.1.0</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>- BE 1.3.2.0 / DB 0.7.2.0 (커밋: a92ca4c)</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SYM-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BUG-079</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Expected Result 가 경고 없이 200자에서 잘린다</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>- 그리드에서 Expected Result 를 200자 넘게 입력하거나 붙여넣으면 200자까지만 들어간다.
+- 잘렸다는 경고가 없다.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>- 길이 제한 없이 입력되고 그대로 저장된다. 백엔드 컬럼은 Text 라 제한이 없다.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>- 201자째부터 사라진 채 저장된다.</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>1. TC 그리드에서 Expected Result 셀을 편집한다.
+2. 200자가 넘는 텍스트를 붙여넣는다.
+3. 셀을 빠져나온 뒤 값을 확인한다.</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>- ag-grid `agLargeTextCellEditor` 는 `cellEditorParams.maxLength` 를 주지 않으면 textarea 에 `maxlength="200"` 을 박는다(`setMaxLength(maxLength || 200)`).</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>원인: - `agLargeTextCellEditor` 를 쓰면서 `cellEditorParams.maxLength` 를 주지 않았다. 라이브러리 기본값 200 이 그대로 걸렸다.
+수정 내용: - `utils/gridEditors.ts` 를 만들어 대용량 텍스트 편집기의 `maxLength` 를 명시한다. 백엔드 컬럼이 Text 이므로 편집기 쪽 제한만 푼다.</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>- 편집기 설정을 `utils/gridEditors.ts` 한 곳으로 모아 컬럼마다 빠뜨리지 않게 했다.</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>- TC 그리드의 Expected Result 등 대용량 텍스트 컬럼 전체.
+- 이미 잘려 저장된 값은 복구되지 않는다.</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>FE 1.3.0.0</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>FE 1.3.1.0 (커밋: b66edeb)</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SYM-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BUG-080</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Remarks 를 편집하면 줄바꿈이 사라진 채 저장된다</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>- 여러 줄로 쓴 비고를 그리드에서 편집하면 줄바꿈이 전부 사라진다.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>- 여러 줄 비고가 줄바꿈을 유지한 채 저장되고, 렌더러가 줄 단위로 보여 준다.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>- 한 줄로 이어붙은 채 저장된다.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>1. Remarks 셀에 두 줄 이상을 넣는다.
+2. 저장 후 다시 편집한다.
+3. 저장된 값에서 줄바꿈이 사라진 것을 확인한다.</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>- Remarks 컬럼에 `cellEditor` 가 없어 기본 편집기 `&lt;input type="text"&gt;` 가 붙었다. HTML 명세상 text input 은 값에서 줄바꿈을 제거한다.
+- 운영 DB 에 줄바꿈이 든 `remarks` 가 0건이었다.
+- 렌더러 `MarkdownCell` 이 값을 `split("\n")` 하는 것을 보면 여러 줄이 전제였다.</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>원인: - Remarks 컬럼에 `cellEditor` 지정이 빠져 단일행 text input 이 붙었다.
+수정 내용: - Remarks 에 대용량 텍스트 편집기를 붙이고 `maxLength` 를 함께 명시한다.</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>- 여러 줄을 전제로 렌더링하는 컬럼은 `utils/gridEditors.ts` 의 같은 편집기를 쓰게 통일했다.</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>- TC 그리드 Remarks 컬럼.
+- 이미 한 줄로 눌린 기존 값은 복구되지 않는다.</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>FE 1.3.0.0</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>FE 1.3.1.0 (커밋: b66edeb)</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SYM-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BUG-081</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>TC ID 자동채우기가 한 행도 채우지 않는데 완료 토스트가 뜬다</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>- 여러 행을 선택해 TC ID 자동채우기를 실행하면 아무 행도 채워지지 않는다.
+- 그런데도 완료 토스트가 뜬다.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>- 선택한 첫 행을 기준점으로 잡고 나머지 행에 이어지는 번호가 들어간다.
+- 채운 행이 없으면 없다고 알린다.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>- 채워진 행이 0개인데 성공으로 보고된다.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>1. TC 그리드에서 TC ID 가 빈 행을 여러 개 선택한다.
+2. TC ID 자동채우기를 실행한다.
+3. 완료 토스트가 뜨지만 TC ID 칸이 그대로인 것을 확인한다.</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>- 선택 행마다 기준점을 다시 잡고 `continue` 해서 실제 대입에 도달하지 않았다.
+- 중복 판단이 화면 행 기준이었다. `getSelectedRows()` 는 필터로 숨은 선택 행까지 돌려주는데(selectedNodes 를 그대로 뱉는다) `allRows` 는 `forEachNodeAfterFilterAndSort` 로 만들어져서, 숨은 행과 ID 가 겹쳐도 경고가 뜨지 않았다.</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>원인: - 순번 계산이 그리드 컴포넌트에 인라인으로 박혀 있었고 테스트가 없었다. 기준점을 행마다 다시 잡는 분기가 남아 있어 아무것도 채우지 못했다.
+수정 내용: - 기준점은 선택 첫 행 하나만 쓰고 나머지를 이어 채운다.
+- 판단 근거를 화면 행에서 전체 행으로 옮기고, 숨어서 건너뛴 선택 행 수를 알려 준다.
+- 되돌릴 수 있게 undo 스택에 넣는다(기존에는 `pushUndo` 호출이 아예 없었다).
+- 행 식별 키를 `(id || no)` 에서 접두사를 붙인 형태로 바꿔 id 와 no 가 같은 숫자일 때의 충돌을 없앴다.
+- 순번 계산을 `utils/tcId.ts` 로 떼어냈다.</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>- `frontend/src/test/tcId.test.ts` 21건. 그리드에 인라인으로 박혀 테스트가 없던 것이 이 결함이 남아 있던 이유다.</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>- TC 그리드의 TC ID 자동채우기, undo 스택.</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>FE 1.3.0.0</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>FE 1.3.1.0 (커밋: b66edeb)</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SYM-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BUG-082</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>행을 여러 개 추가하면 전부 같은 순번과 TC ID 를 받는다</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>- 대량 추가로 30행을 넣으면 30행이 전부 같은 `no` 와 같은 TC ID 를 갖는다.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>- 추가한 행마다 순번과 TC ID 가 1씩 이어진다.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>- 모든 행이 같은 값을 받아, 저장하면 TC ID 중복이 된다.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>1. TC 그리드에서 행 대량 추가를 연다.
+2. 30행을 추가한다.
+3. 추가된 행들의 순번과 TC ID 를 확인한다.</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>- 대량 추가가 `await` 루프로 `handleAddRow` 를 부르는데, 렌더 시점 `rowData` 를 클로저로 잡아 `nextNo` 가 루프 내내 같았다.
+- 접두사도 기존 행에서 가져오지 않고 `"TC-"` 로 고정돼 있었다.</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>원인: - 한 행 추가 함수를 루프로 부르면서 다음 순번을 클로저에 잡힌 옛 `rowData` 에서 계산했다.
+수정 내용: - `addRows(count)` 로 합쳐 다음 순번을 루프 밖에서 한 번만 계산한다.
+- 접두사를 기존 행에서 가져온다.</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>- 순번 계산이 `utils/tcId.ts` 로 빠지면서 같은 테스트 21건이 이 경로도 덮는다.</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>- TC 그리드 행 추가와 대량 추가.
+- 이 경로로 만들어져 이미 저장된 중복 TC ID 는 마이그레이션 `b7d3c9a1e450` 이 `-2`, `-3` 으로 정리한다.</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>FE 1.3.0.0</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>FE 1.3.1.0 (커밋: b66edeb)</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SYM-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>BUG-083</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>시트가 하나인 프로젝트에서 행을 추가하면 `기본` 시트가 조용히 생긴다</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>- 시트가 하나뿐인 프로젝트를 열고 바로 행을 추가하면, 만든 적 없는 `기본` 시트가 생기고 행이 그쪽으로 들어간다.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>- 시트가 하나면 그 시트가 선택된 상태여야 하고, 행은 그 시트에 들어간다.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>- `기본` 시트가 새로 만들어지고 행이 원래 시트에 보이지 않는다.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>- 프로젝트에 시트가 하나만 있다.</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>1. 시트가 하나인 프로젝트를 연다.
+2. 시트를 직접 클릭하지 않고 바로 행을 추가한다.
+3. 시트 목록에 `기본` 이 생긴 것을 확인한다.</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>- 시트 자동 선택 조건이 `flatAll.length &gt; 1` 이라 시트가 하나면 로드 직후 `activeSheet` 가 null 이었다.
+- 그 상태의 행 추가가 `sheet_name` 을 `기본` 으로 보내고 백엔드가 그 시트를 만들었다(`sheets.py` `auto_create_default`).</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>원인: - 시트 자동 선택 조건이 하나짜리 프로젝트를 빠뜨렸다.
+수정 내용: - 자동 선택 조건을 고쳐 시트가 하나여도 선택되게 했다.
+- `전체` 보기에서는 행 추가 버튼을 막는다.</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>- `전체` 보기에서 추가를 막아 시트가 정해지지 않은 상태로는 행을 만들 수 없게 했다.</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>- 시트가 하나인 프로젝트의 행 추가.</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>FE 1.3.0.0</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>FE 1.3.1.0 (커밋: b66edeb)</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SYM-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>BUG-084</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>자동 저장이 실패해도 이유를 알려주지 않는다</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>- 그리드 자동 저장이 실패하면 `자동 저장 실패` 만 뜬다. 서버가 준 사유가 화면에 나오지 않는다.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>- 서버가 준 `detail` 을 사용자 언어로 보여 준다. TC ID 중복이면 어느 ID 가 겹쳤는지 알 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>- 무엇을 고쳐야 하는지 알 수 없어 같은 편집을 반복하게 된다.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>1. 이미 쓰이는 TC ID 를 다른 행에 입력한다.
+2. 자동 저장이 도는 것을 기다린다.
+3. 토스트 문구를 확인한다.</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>- 자동 저장 실패 경로가 서버 응답의 `detail` 을 읽지 않고 고정 문구만 띄웠다.</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>원인: - 오류 처리에서 응답 본문을 버리고 고정 문구를 썼다.
+수정 내용: - 서버가 준 `detail` 을 `translateError` 로 옮겨 띄운다.
+- `utils/errorMessage.ts` 에 TC ID 중복 409 문구를 추가하고 ko/en 사전에 넣었다.</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>- 백엔드가 이 경우 500 이 아니라 409 와 안내 문구를 돌려주도록 함께 고쳤다(a92ca4c).</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>- TC 그리드 자동 저장 오류 표시, ko/en 번역 사전.</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>FE 1.3.0.0</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>FE 1.3.1.0 (커밋: b66edeb)</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SYM-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BUG-085</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>그리드 헤더의 필터 버튼이 배경과 대비가 없어 보이지 않는다</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>- 그리드 헤더의 필터 버튼이 사실상 검정 위 검정이라 어디를 눌러야 필터가 열리는지 보이지 않는다.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>- 라이트와 다크 양쪽에서 헤더 글자와 같은 수준으로 읽힌다.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>- 대비 약 1.1:1. 버튼이 있는지조차 알 수 없다.</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>1. TC 그리드를 연다.
+2. 헤더 셀에 마우스를 올린다.
+3. 필터 버튼을 찾아본다.</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>- `.ag-header-cell-filter-button` 이 `--ag-foreground-color` 를 따라가 `#1A1D23` 으로 칠해졌다. 헤더 배경은 `#1E293B` 라 대비 약 1.1:1.
+- 같은 헤더의 필터 걸림 표시(`.ag-icon-filter`)는 헤더 전경색을 제대로 받고 있어서 버튼만 빠져 있었다.</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>원인: - 필터 버튼이 헤더 전경색이 아니라 본문 전경색 변수를 따라갔다.
+수정 내용: - `--ag-header-foreground-color` 를 따라가게 해서 라이트와 다크 양쪽에서 자동으로 맞는다(실측 13.35:1 / 15.01:1).
+- 아이콘이 `mask-image` + `background-color` 로 그려지므로 `::before` 도 같이 지정한다.
+- 평소 `opacity` 0.7, 셀 호버 시 1 로 올려 헤더 글자를 가리지 않게 했다.
+- 필터가 걸린 열은 파란색으로 칠해 어느 열에 필터가 있는지 바로 보이게 했다.</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>- 색을 고정값이 아니라 헤더 전경색 변수에 묶어 테마를 바꿔도 따라온다.</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>- 그리드 헤더 필터 버튼 전체(라이트, 다크).</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>FE 1.3.0.0</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>FE 1.3.1.0 (커밋: b554e86)</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SYM-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>BUG-086</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>blocker</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>alembic head 가 둘로 갈라져 앱이 기동하지 못한다</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>- 백엔드가 기동하지 못한다. `Multiple head revisions are present` 로 마이그레이션이 실패한다.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>- `alembic upgrade head` 가 단일 head 로 통과하고 앱이 뜬다.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>- 마이그레이션이 lifespan 안에서 터져 앱이 아예 뜨지 않는다. 우회 경로가 없다.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>1. `b7d3c9a1e450` 이 포함된 커밋을 받는다.
+2. 백엔드를 기동한다.
+3. `Multiple head revisions are present` 를 확인한다.</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>- 원격에 `05f8800a57f5`(account_requests)와 `a1c4e7b9d2f0`(test_results 유니크)이 먼저 올라가 있었다.
+- `b7d3c9a1e450` 의 `down_revision` 이 `06933fddb519` 이라 둘 다 같은 부모에서 갈라져 head 가 두 개가 됐다.</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>원인: - 마이그레이션을 로컬에서 만들 때 부모를 원격 최신 head 가 아니라 그 앞 리비전으로 잡았다.
+수정 내용: - `down_revision` 을 `a1c4e7b9d2f0` 으로 바꿔 체인 맨 뒤에 붙인다.</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>- 체인이 `8925bb1ad2db` -&gt; `06933fddb519` -&gt; `05f8800a57f5` -&gt; `a1c4e7b9d2f0` -&gt; `b7d3c9a1e450` 단일 선형인 것을 확인했다.
+- 마이그레이션이 lifespan 에서 자동 실행되므로 여기서 실패하면 앱 전체가 못 뜬다. 새 마이그레이션은 `alembic heads` 가 하나인지 보고 만든다.</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>- 백엔드 기동 전체.</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>DB 0.7.2.0</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>DB 0.7.2.0 (커밋: a1f525e)</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SYM-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SEC-014</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>로컬 자격증명 파일과 QA 스크래치 스크립트가 gitignore 에 없다</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>- `ym-testcase-credentials.txt` 와 `frontend/_*.mjs` 가 untracked 인데 무시 대상이 아니었다.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>- 평문 계정 정보가 든 로컬 파일은 `git add -A` 로도 올라가지 않는다.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>- `git add -A` 한 번에 공개 저장소로 올라갈 수 있는 상태였다.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>1. 저장소 루트에서 `git status --porcelain` 을 본다.
+2. `ym-testcase-credentials.txt` 와 `frontend/_*.mjs` 가 `??` 로 잡히는 것을 확인한다.</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>- 스크래치 스크립트 17개 중 14개에 평문 비밀번호와 계정 문자열이 들어 있었다.
+- 원격은 공개 저장소다.
+- 히스토리에 커밋된 적은 없음을 확인했다. 실제 유출은 없었다.</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>원인: - QA 작업 중 만든 로컬 파일들이 `.gitignore` 에 반영되지 않았다.
+수정 내용: - `.gitignore` 에 `ym-testcase-credentials.txt` 와 `frontend/_*.mjs` 를 포함한 5줄을 추가한다.</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>- 스크래치 파일 이름 규칙(`_` 접두사)을 통째로 무시 대상에 넣어 다음 파일도 자동으로 걸린다.</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>- 저장소 전체. 이미 푸시된 내용은 없다.</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>System 1.3.1.0</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>System 1.3.2.0 (커밋: 160e924)</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SYM-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>BUG-087</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>trivial</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>package-lock 버전이 package.json 과 어긋난다</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>- `frontend/package-lock.json` 의 `version` 이 `package.json` 과 다르다. npm 을 실행할 때마다 lock 이 조용히 다시 쓰인다.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>- 두 파일의 `version` 이 같아 npm 실행이 lock 을 건드리지 않는다.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>- lock 이 `1.0.3.0` 에 머물러 있다가 npm 실행 시 `1.2.2.0` 으로 바뀌었고, `package.json` 은 `1.3.1.0` 이라 여전히 어긋났다.</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>1. `frontend/package.json` 과 `frontend/package-lock.json` 의 `version` 을 비교한다.
+2. `npm install` 을 돌린 뒤 `git status` 로 lock 이 변경되는지 본다.</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>- 커밋 `fdc6e5f` 시점 diff: lock `1.0.3.0` -&gt; `1.2.2.0`, 같은 시점 `package.json` 은 `1.3.1.0`.</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>원인: - 릴리즈마다 `package.json` 만 올리고 lock 을 같이 올리지 않았다. 의존성 변경은 없다.
+수정 내용: - lock 의 두 `version` 필드를 `package.json` 과 같은 값으로 맞춘다.</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>- 버전 올릴 때 `package.json` 과 lock 의 두 자리를 함께 고친다.</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>- 프론트엔드 빌드 메타데이터. 의존성 트리는 그대로다.</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>FE 1.3.0.0</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>FE 1.3.1.0 (커밋: fdc6e5f)</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SYM-33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9849,7 +11057,6 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -9907,7 +11114,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U147"/>
+  <dimension ref="A1:U148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10976,6 +10976,127 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>BUG-088</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>pytest 수집 단계에서 engine 이 개발용 DB 에 묶여 CI 백엔드 잡이 전부 실패한다</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>- CI 의 Backend(pytest) 잡이 223 errors 로 실패한다.
+- `RuntimeError: Server did not start within 15s at http://127.0.0.1:8008/docs`
+- 로컬(Windows)에서는 서버가 뜨지만 login 이 401 로 떨어져 184 errors.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>- 백엔드 스위트가 임시 DB 에서 격리되어 돌고, 개발용 `tc_manager.db` 에 쓰기가 들어가지 않는다.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>- 마이그레이션은 임시 DB 로 가고 앱 세션은 개발용 DB 를 본다.
+- CI 는 테이블이 없는 빈 DB 를 보고 기동에 실패한다.
+- 로컬은 개발 DB 를 그대로 써서 admin 비밀번호가 테스트 값과 달라 401 이 난다.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>1. `cd backend`
+2. 8008 에 개발 서버가 없는 상태로 `python -m pytest -q`
+3. 서버가 필요한 테스트가 전부 setup 단계에서 에러가 되는 것을 확인한다.</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>- CI run 34101117538, 34118964885 둘 다 같은 지점에서 실패.
+- CI 로그의 alembic 이 `-&gt; 8925bb1ad2db` 부터 전 체인을 돈다. 즉 마이그레이션 대상은 빈 임시 DB 다.
+- 로컬 실측: 수정 전 184 errors, 수정 후 249 passed / 1 skipped.
+- `database.py:9,16` 은 임포트 시점에 `DATABASE_URL` 을 읽어 engine 을 만든다.
+- `main.py:45` 의 lifespan 은 실행 시점 `os.getenv` 를 읽는다.</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>- 배치 로그 (GitHub Actions CI)</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>원인: - 2026-09-07 커밋 a92ca4c 가 추가한 `tests_unit/test_tc_id_dedup.py` 가 모듈 수준에서 `from models import ...` 를 한다. pytest 는 수집 단계에서 테스트 모듈을 전부 임포트하므로 그 시점에 `database.py` 가 임포트되며 engine 이 기본값인 개발용 `./tc_manager.db` 에 묶인다.
+- `conftest.py::_server` 가 `os.environ["DATABASE_URL"]` 을 임시 DB 로 바꾸는 것은 수집이 끝난 뒤라 늦다. 그래서 lifespan 과 앱 세션이 서로 다른 DB 를 본다.
+- CI 는 개발 DB 파일이 없어 테이블 없는 빈 DB 가 만들어지고 `main.py:58` 의 `_purge_old_deleted_testcases()` 가 터져 기동 자체가 실패한다.
+수정 내용: - `conftest.py` 임포트 시점에 임시 DB 를 만들어 `DATABASE_URL` 에 박는다. conftest 는 어떤 테스트 모듈보다 먼저 임포트되므로 여기가 유일하게 안전한 자리다.
+- 셸에 개발 DB 가 박혀 있어도 임시 DB 로 돌린다. 일부러 쓰려면 `ALLOW_DEV_DB=1` (`test_run_tc_sync.py` 가 이미 쓰는 opt-in 이름을 그대로 쓴다).
+- 서버가 이미 떠 있으면 `DATABASE_URL` 을 건드리지 않는다. HTTP 는 그 서버의 DB 로 가는데 in-process engine 만 임시 DB 로 돌리면 `test_account_requests.py` 처럼 HTTP 로 쓰고 `SessionLocal` 로 읽는 테스트가 깨진다.
+- `_server` 픽스처는 더 이상 `DATABASE_URL` 을 덮어쓰지 않는다.</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>- `backend/test_db_isolation.py` 5건. 서브프로세스로 임포트 순서를 직접 재현하므로 수집 순서에 기대지 않는다. 이 파일만 단독 실행해도 결함을 잡는다.
+- 뮤테이션으로 이빨을 확인했다. 격리 블록을 무력화하면 3건, 서버 분기 가드를 무력화하면 1건이 실패한다.
+- QA 2인(Codex 읽기전용 + 자체 리뷰 에이전트) 교차 검증. 두 보고가 독립적으로 같은 Major 2건(서버 분기 DB 분리, 약한 가드)을 지적했고 둘 다 반영했다.</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>- 백엔드 테스트 스위트와 CI 의 Backend(pytest) 잡. 제품 런타임 동작은 바뀌지 않는다.
+- 이 결함이 살아 있는 동안 개발용 `tc_manager.db` 에 쓰기가 들어갈 수 있었다.</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>BE 1.3.2.0</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>- BE 1.3.2.1</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SYM-34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U148"/>
+  <dimension ref="A1:U149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11097,6 +11097,107 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>BUG-089</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>자동저장이 거부된 값이 그리드에 남아 그 행의 이후 편집이 전부 실패한다</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>- TC ID 를 이미 쓰이는 값으로 바꾸면 서버가 409 로 거부하는데, 거부된 값이 그리드에 그대로 남는다.
+- 그 뒤로 같은 행의 다른 칸을 고쳐도 매번 같은 409 가 나고 아무것도 저장되지 않는다.
+- 그 행은 새로고침 전까지 편집이 막힌다.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>- 저장이 거부되면 그 칸을 서버 값으로 되돌린다.
+- 되돌리지 않더라도, 같은 행의 다른 칸 편집은 저장돼야 한다.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>- 화면은 `DUP-001`, DB 는 `DUP-002` 로 갈라진다.
+- 이어서 Category 를 고치면 자동저장이 행 전체를 보내면서 중복 TC ID 가 다시 실려 또 409 가 난다.
+- 오류 토스트를 못 보고 지나가면 저장된 줄 알게 된다.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>- 한 프로젝트에 TC 가 둘 이상 있다.
+- TC ID 유니크 제약이 걸린 v1.3.2.0 이상.</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>1. TC 두 건이 있는 프로젝트의 TC 관리 화면을 연다(예: `DUP-001`, `DUP-002`).
+2. 두 번째 행의 TC ID 를 `DUP-001` 로 고치고 Enter 를 누른다.
+3. `이미 쓰이는 TC ID입니다.` 토스트를 확인한다.
+4. 그리드의 두 번째 행 TC ID 칸이 여전히 `DUP-001` 인 것을 확인한다.
+5. 같은 행의 Category 를 아무 값으로 고치고 Enter 를 누른다.
+6. 같은 409 문구가 다시 뜨고 Category 가 저장되지 않는 것을 확인한다.</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>- 실측 2026-09-07, 새 DB 로 띄운 서버(백엔드 1.3.2.1, 프론트 1.3.2.1).
+- 거부 직후 화면 값 `DUP-001`, 같은 시각 API 조회 결과 `no=2 tc_id=DUP-002`.
+- 이어서 Category 를 `수정시도` 로 고친 뒤 API 조회 결과 `category=검증` (미반영).
+- 새로고침 후에는 화면이 `DUP-002` 로 돌아오고 Category 편집이 정상 저장된다(`category=회복확인`).</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>- QA (v1.3.2.0 수정 항목 검증 중)</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>FE 1.3.1.0</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SYM-35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -11182,14 +11182,52 @@
           <t>- QA (v1.3.2.0 수정 항목 검증 중)</t>
         </is>
       </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>자동저장이 실패해도 화면 값을 되돌리는 곳이 없었다. 자동저장은 행 전체를
+보내므로 거부된 값이 그대로 남으면 같은 행의 다음 편집도 그 값을 다시 실어 보내
+계속 같은 이유로 거부된다.
+- 행마다 서버가 확정한 마지막 상태를 들고 있다가(`lastSavedRef`), 저장이 거부되면
+  그 상태로 되돌린다(`restoreRow`).
+- 되돌리기를 편집 지점이 아니라 자동저장 한 곳에 뒀다. `autoSaveRow` 를 부르는
+  경로는 여섯인데(셀 편집, 찾기/바꾸기, 일괄 변경, TC ID 자동채우기, Ctrl+D 채우기,
+  undo/redo) 다섯은 `node.data` 를 직접 고쳐 `onCellValueChanged` 를 타지 않는다.
+  편집 쪽에 기록을 붙인 첫 구현은 그 다섯을 놓쳤고, QA 2인이 독립적으로 같은
+  지적을 했으며 E2E 로 재현했다.
+- 스냅샷은 `rowData` 가 바뀔 때만 다시 잡는다. 사라진 행의 스냅샷은 같이 버려져
+  시트나 프로젝트를 옮겨도 남지 않는다.
+- 되돌릴 때 같은 객체를 채운다. 새 객체로 갈아끼우면 `rowData` state 와 그리드가
+  갈라진다.</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>- E2E 2건 추가(`tc-management.spec.ts`). 셀 편집 경로와 모두 바꾸기 경로 각각의
+  거부를 덮는다. CI 가 이 파일을 돌린다.
+- 뮤테이션으로 이빨을 확인했다. `restoreRow` 호출을 막으면 2건 다 실패한다.
+- 첫 구현으로는 모두 바꾸기 테스트가 실패했다. 그 실패가 경로 누락을 잡아냈다.</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>- TC 관리 그리드의 자동저장 실패 처리 전체(셀 편집, 찾기/바꾸기, 일괄 변경,
+  TC ID 자동채우기, Ctrl+D 채우기, undo/redo).
+- 저장이 거부되면 입력값이 화면에서 사라지고 서버 값으로 돌아간다.</t>
+        </is>
+      </c>
       <c r="R149" t="inlineStr">
         <is>
           <t>FE 1.3.1.0</t>
         </is>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>FE 1.3.2.0</t>
+        </is>
+      </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U149"/>
+  <dimension ref="A1:U150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11236,6 +11236,132 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>BUG-090</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>테스트 수행 그리드에서 첨부파일이 있어도 셀을 눌러야 보인다</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 그리드의 첨부 컬럼이 어느 행이든 + 버튼만 보인다.
+- 그 행을 클릭해야 그때 파일명이 나타난다. 클릭 전에는 첨부가 있는지 없는지 알 수 없다.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>- 런을 열면 첨부가 있는 행에 파일명이 바로 보인다.
+- 첨부 유무를 확인하려고 행을 하나씩 눌러 볼 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>- 첨부가 있는 행도 + 버튼만 그려진다.
+- 첨부가 있는 행과 없는 행이 화면상 구별되지 않는다.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>- 결과 행에 첨부파일이 하나 이상 있는 테스트 수행이 존재한다.</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>1. 테스트 수행 화면에서 결과 행에 이미지를 첨부한다.
+2. 페이지를 새로고침하거나 다른 런을 갔다가 그 런으로 돌아온다.
+3. 첨부 컬럼을 클릭하지 않은 상태로 그리드를 본다.</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>- frontend/src/hooks/useAttachments.ts 의 attachmentsMap 은 빈 객체로 시작한다.
+- TestRunManager.tsx 의 onRowFocused 만 loadAttachmentFor(rowId) 를 부른다. 즉 그 행을 클릭해야 채워진다.
+- 셀 렌더러는 attachmentsMap[row.id] 가 없으면 빈 배열로 읽어 + 버튼만 그린다.</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>원인: 첨부 맵(useAttachments.attachmentsMap)이 빈 채로 시작하고, 행 포커스 때만 loadAttachmentFor 로 한 행씩 채웠다. 셀 렌더러는 값이 없으면 빈 배열로 읽어 + 버튼만 그린다.
+수정:
+- GET /api/attachments/by-run/{run_id} 추가. 런 하나의 첨부를 TestResult 조인으로 한 번에 반환한다.
+- loadRunDetail 에서 런 상세를 받은 뒤 seedAttachments 로 모든 결과 행을 채운다. 실패하면 기존 lazy 로더로 폴백한다.
+- QA 교차검증에서 나온 경합 2건도 같이 잡았다. 맵을 통째로 갈아끼우지 않고 병합해 조회 중 올리거나 지운 첨부가 되돌아가지 않게 했고, 런 상세 요청에 세대 번호를 붙여 늦게 온 이전 런의 응답을 버린다.
+- attachments.test_result_id 인덱스 추가. 조회가 첨부 테이블 전체 스캔을 타고 있었다.</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>- frontend/src/test/TestRunAttachments.test.tsx 신규 5건. ag-grid 를 자체 모킹해 첨부 컬럼 cellRenderer 를 실제로 실행한다. 클릭 없이 파일명이 보이는지, stale 응답이 화면을 덮지 않는지를 본다.
+- frontend/src/test/useAttachments.test.tsx 신규 4건. 업로드/삭제와 일괄 조회의 경합을 고정한다.
+- backend/test_attachment_bulk.py 신규 4건. 일괄 조회, 런 경계 격리, 404, 미인증 거부.
+- 회귀 체크리스트 TC-TR-037 추가(첨부 목록 표시).
+- 수정을 되돌려 새 테스트가 실제로 실패하는지 확인했다.
+- 하지 않을 것: 공용 ag-grid 모킹으로 가려진 다른 컬럼(Result 드롭다운, 단축키, Ctrl+D 채우기, undo)의 렌더러 테스트는 이번 범위에서 뺐다.</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 화면의 첨부 컬럼 표시.
+- 첨부 조회 API. 런을 여는 동안 요청이 행 수만큼에서 1회로 줄었다.
+- DB 스키마(attachments 인덱스 1건 추가). 마이그레이션은 서버 기동 시 자동 적용된다.</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>FE 1.3.2.0</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>FE 1.3.3.0 / BE 1.3.3.0 / DB 0.7.3.0</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SYM-36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U150"/>
+  <dimension ref="A1:U154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11362,6 +11362,445 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ENH-046</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>테스트 수행을 시트 단위로 만들 수 없다</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>- 새 테스트 수행을 만들면 프로젝트의 모든 TC 가 담긴다.
+- 담을 시트를 고르는 수단이 없다. 만든 뒤에는 시트 탭으로 보기만 걸러진다.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>- 생성 모달에서 담을 시트를 고른다. 처음에는 전부 선택돼 있고 체크를 풀어 줄인다.
+- 고른 시트의 TC 만 수행에 담긴다.
+- 고른 범위가 수행에 저장되어, 진행 중 수행이 새 TC 를 흡수할 때도 그 범위를 지킨다.
+- 수행 상세의 시트 탭은 그 수행의 범위만 보여 준다.</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>- [x] 생성 모달에서 시트를 고를 수 있다. 기본은 전체 선택이고 체크 해제로 줄인다.
+- [x] 전부 해제하면 생성할 수 없다.
+- [x] 고른 시트의 TC 만 결과 행으로 만들어진다.
+- [x] 범위를 수행에 저장하고, 새 TC 흡수 시에도 지킨다.
+- [x] 수행을 복제하면 범위도 따라간다.
+- [x] 폴더와 없는 시트는 범위로 받지 않는다.
+- [x] 범위 밖 TC 의 결과 제출을 거부한다.
+- [x] 시트 탭이 그 수행의 범위만 보여 준다.
+- [x] 사용자 매뉴얼 갱신.</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>- 시트가 여러 개인 프로젝트에서 한 영역만 회귀 돌릴 때, 전체 TC 가 담긴 수행에서 다른 시트가 계속 미실행으로 남아 진행률이 실제와 다르게 보인다.
+- 라운드를 영역별로 나눠 돌리는 운영을 지금 방식으로는 표현할 수 없다.</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>- 생성 모달에 시트 체크박스를 넣고, 고른 시트를 test_runs.sheet_names (JSON, nullable) 에 저장한다. NULL 은 프로젝트 전체를 뜻해 기존 수행과 동작이 같다.
+- 생성 시점의 필터가 아니라 수행의 범위로 다룬다. run_sync_service.sync_run_results 에서도 같은 조건을 건다. 걸지 않으면 TC 하나가 생기는 순간 제외한 시트가 통째로 들어온다(재현 테스트로 확인).
+- QA 교차검증에서 나온 우회 경로 3건을 같이 막았다. 결과 제출(submit_results)이 시트 범위를 안 봐서 API 한 번으로 범위 밖 TC 가 들어오던 것, 폴더를 범위로 지정할 수 있던 것, 중복 시트명이 그대로 저장되던 것.
+- 시트 탭이 트리 루트만 보고 있어 폴더 밑 시트로 범위를 잡으면 탭이 하나도 안 나오던 것도 고쳤다.
+- 2차 QA 교차검증 대응: 시트 이름을 바꾸면 런 범위가 아무것도 가리키지 않게 되어 그 수행의 결과 저장이 전부 거부되고 새 TC 도 흡수되지 않던 것을 고쳤다(rename 과 같은 트랜잭션에서 범위도 치환). 시트 삭제 시에도 범위에서 뺀다. 이때 범위가 빌 수 있어 '없음' 과 '전체' 를 is not None 으로 갈랐다. 빈 목록이 falsy 로 떨어지면 담을 것이 없어진 수행이 프로젝트 전체를 담는다.</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>- backend/test_run_sheet_scope.py 10건. 범위 적용, 미지정 시 전체, 신규 TC 흡수의 범위 유지, 복제 승계, 폴더 거부, 없는 시트 400, 빈 목록 400, 중복 제거, 범위 밖 결과 제출 거부, 대시보드 분모.
+- frontend/src/test/TestRunSheetScope.test.tsx 7건.
+- 회귀 체크리스트 TC-TR-038, TC-TR-039 추가.
+- 동기화 가드와 페이로드 전달을 각각 되돌려 테스트가 실제로 실패하는지 확인했다.
+- 하지 않을 것: 이미 만든 수행의 범위를 나중에 바꾸는 기능, 테스트 플랜과의 연동.
+- 2차: 시트 rename 후 범위 유지, 삭제된 TC 결과의 대시보드 분자 제외 테스트 2건 추가(총 12건).</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 생성/복제/결과 제출, 수행 상세의 시트 탭.
+- test_runs 테이블에 컬럼 1개 추가.
+- 사용자 매뉴얼 8-1 절.</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>FE 1.3.3.0</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>FE 1.4.0.0 / BE 1.4.0.0 / DB 0.8.0.0</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SYM-37</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>BUG-091</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>대시보드가 프로젝트 전체 TC 를 분모로 써서 일부 시트만 담은 수행의 진행률이 틀리다</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>- 일부 시트만 담은 테스트 수행을 대시보드에서 고르면 총 건수가 그 수행이 담은 TC 수가 아니라 프로젝트 전체 TC 수로 나온다.
+- 그 수행의 TC 를 전부 PASS 로 입력해도 진행률이 100% 에 닿지 않고 미실행이 남는다.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>- 수행을 골랐을 때 총 건수는 그 수행이 담은 TC 수다.
+- 그 수행을 전부 수행하면 진행률 100%, 미실행 0 이다.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>- 결제 시트 4건을 전부 PASS 했는데 total 11, not_started 7, pass_rate 36.4 로 나왔다.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>- 시트가 여러 개인 프로젝트에 일부 시트만 담은 테스트 수행이 있다.</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>1. 시트 3개짜리 프로젝트에서 시트 하나만 골라 테스트 수행을 만든다.
+2. 그 수행의 TC 를 전부 PASS 로 입력한다.
+3. 대시보드에서 그 수행을 고른다.</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>- 실측 2026-09-08, GET /api/projects/{id}/dashboard/summary?run_id={run} 응답:
+  {"total": 11, "pass": 4, "not_started": 7, "pass_rate": 36.4}
+- dashboard.py 의 total 은 TestCase 를 project_id 로만 세고, run_id 분기는 그 값을 그대로 분모로 쓴다.
+- priority, category, rounds, overview 도 같은 방식이다.</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰 (SYM-37 시트 범위 기능 QA 교차검증)</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>원인: 대시보드가 총 건수를 TestCase 에서 project_id 로만 세고, run_id 분기는 그 값을 그대로 분모로 썼다. 시트 범위 기능이 생기기 전에는 프로젝트 전체 TC 수와 수행이 담은 TC 수가 항상 같아서 드러나지 않았다.
+수정: run_id 가 오면 그 수행의 결과 행에 들어 있는 TC 로 총계를 좁힌다. summary, priority, category 에 적용했고, rounds 는 라운드별 대표 수행의 결과 행 수를 분모로 쓴다. 전역 개요는 최신 수행이 담은 행 수를 분모로 쓴다(수치가 그 수행에서 나오므로 분모도 같아야 한다).
+- 2차 QA 대응: summary 와 rounds 의 분자도 활성 TC 로 좁혔다. 분모만 좁히면 지운 TC 의 결과가 남아 pass 가 total 을 넘는다. rounds 와 전역 개요에서 결과 행이 0 인 런이 프로젝트 전체로 되돌아가던 fallback 도 고쳤다.</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>- backend/test_run_sheet_scope.py 의 대시보드 테스트 1건. summary, category, priority 를 함께 본다.
+- 회귀 체크리스트 TC-TR-040 추가.
+- 수정을 되돌려 테스트가 실패하는지 확인했다.
+- reports.py 와 testplans.py 는 TestResult 행 수를 직접 세는 방식이라 손대지 않았다.</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>- 대시보드 summary, priority, category, rounds 와 전역 개요.
+- 일부 시트만 담은 수행의 수치가 달라진다(실측 36.4% -&gt; 100%).</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>BE 1.3.3.0</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>BE 1.4.0.0</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SYM-38</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>BUG-092</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>pre-Alembic DB 를 stamp(head) 로만 처리해 새 컬럼이 없는 채로 최신 버전이 된다</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>- 테이블은 있는데 alembic_version 테이블이 없는 DB 를 만나면 main.py 의 lifespan 이 stamp(head) 만 한다.
+- 실제 스키마는 그대로인데 버전만 최신으로 찍혀, 이후 어떤 마이그레이션도 적용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>- 스키마와 alembic 버전이 어긋나지 않는다. 또는 어긋난 것을 감지해 기동을 멈추고 알린다.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>- 이후 ORM 이 새 컬럼(예: test_runs.sheet_names)을 조회하면 no such column 으로 실패한다.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>- Alembic 도입(v1.2.1.0) 이전에 만들어져 계속 쓰이는 DB 파일.</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>1. alembic_version 테이블이 없고 다른 테이블은 있는 tc_manager.db 를 준비한다.
+2. 서버를 기동한다.
+3. sqlite 로 test_runs 스키마를 확인한다.</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>- 미확인</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>- backend/main.py 의 lifespan: tables and "alembic_version" not in tables 이면 alembic_command.stamp(cfg, "head") 만 부른다.
+- 이 경로에는 컬럼을 만드는 단계가 없다.</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰 (SYM-37 QA 교차검증, Codex)</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>BE 1.3.3.0</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SYM-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>BUG-093</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>테스트 수행에서 결과 저장이 거부돼도 이유를 알 수 없고 화면 값이 그대로 남는다</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>- 결과 저장이 서버에서 거부되면 이유와 무관하게 '저장 실패' 만 뜬다.
+- 화면의 셀 값은 바뀐 채로 남아 저장된 것처럼 보인다. 새로고침하면 서버 값으로 돌아간다.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>- 서버가 준 거부 사유를 그대로 보여 준다.
+- 거부된 값은 화면에서도 서버 값으로 되돌아간다.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>- catch 블록이 예외를 버리고 고정 문구만 띄운다.
+- 되돌리는 코드가 없어 화면과 DB 가 갈라진다.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>- 결과 저장이 거부되는 상황. 시트 범위 밖 TC 제출이 이번에 새로 생긴 거부 경로다.</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>1. 시트를 골라 테스트 수행을 만든다.
+2. 범위 밖 TC 의 결과를 저장하는 요청이 나가게 한다.
+3. 화면의 값과 서버 값을 대조한다.</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>- TestRunManager.tsx 의 saveOneResult, saveManyResults 가 catch 에서 toast.error(t('saveFailed')) 만 부른다.
+- 같은 레포 ProjectSettings.tsx 는 err.response.data.detail 을 꺼내 쓴다. 패턴이 갈려 있다.
+- SYM-35 가 TC 관리 그리드에서 같은 유형으로 이미 한 번 났다.</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰 (SYM-37 QA 교차검증 2차)</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>원인: saveOneResult 와 saveManyResults 의 catch 가 예외를 버리고 고정 문구만 띄웠다. 되돌리는 코드도 없어 거부된 값이 화면에 남았다.
+수정: 공용 handleSaveError 로 모아 서버가 준 detail 을 그대로 띄우고, 실패하면 런 상세를 다시 받아 화면을 서버 값으로 되돌린다.</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>- frontend/src/test/TestRunSaveError.test.tsx 4건. ag-grid 를 자체 모킹해 onCellValueChanged 저장 경로를 실제로 태운다. detail 노출, 실패 시 재조회, detail 이 없을 때 기본 문구, 성공 시 재조회 안 함.
+- 옛 처리로 되돌려 2건이 실패하는지 확인했다.
+- 하지 않을 것: 셀 단위 롤백은 넣지 않았다. 런 상세를 다시 받는 편이 경로가 하나라 어긋날 여지가 적다.</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 그리드의 결과/실제결과/이슈링크/비고 저장 실패 처리 전체.</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>FE 1.3.3.0</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>FE 1.4.0.0</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SYM-40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U154"/>
+  <dimension ref="A1:U162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11801,6 +11801,776 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>BUG-094</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>시트를 골라 만든 테스트 수행의 No 가 1 부터 시작하지 않는다</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>- 시트를 골라 만든 수행을 열면 No 컬럼이 4, 5, 6, 51 처럼 나온다
+- 시트가 둘 이상인 프로젝트의 수행도 기본 탭(첫 시트)에서 같은 증상이 난다</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>- No 는 지금 보고 있는 목록의 순번이라 1 부터 이어져야 한다</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>- TC 에 저장된 no 가 그대로 나온다. 프로젝트 118 의 수행 34(결제 시트)에서 4, 5, 6, 51</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>1. 시트가 둘 이상인 프로젝트에서 시트 하나만 골라 수행을 만든다
+2. 그 수행을 연다
+3. No 컬럼을 본다</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>- 실 DB 조회: 수행 34 의 TC no 가 4, 5, 6, 51
+- 브라우저 실측: No 컬럼 값이 4, 5, 6, 51</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>원인: - TestRunManager.tsx 의 loadRunDetail 이 재번호를 '전체' 탭 경로에서만 한다
+- 시트가 둘 이상이면 기본 탭이 첫 시트이고, 시트를 골라 만든 수행은 전체 탭 자체가 없다. 실제로 보게 되는 화면이 대부분 재번호 없는 쪽이었다
+- 전체 탭 분기의 조건도 트리 루트 개수라, 시트를 폴더 하나에 모아 둔 프로젝트는 전체 탭에서도 재번호가 걸리지 않았다
+수정 내용: - 시트 탭과 전체 탭을 한 경로로 합쳐 항상 1 부터 매긴다
+- 시트 순서를 트리 루트가 아니라 펴 놓은 잎 시트에서 가져온다
+- 기본 탭도 잎 시트로 고른다. 루트 첫 칸이 폴더면 폴더 이름으로 걸러 그리드가 빈 채로 열리고 상세를 두 번 받았다
+- 서버가 준 객체를 제자리에서 고치지 않고 새 객체로 바꿔 저장된 no 를 건드리지 않는다</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>- TestRunNumbering.test.tsx 8건. 시트 범위 수행, 시트 탭, 폴더로 묶은 프로젝트, 시트 목록이 늦게 오는 경우, 저장된 no 불변까지 본다
+- 번호만 보면 시트 순서가 틀려도 1,2,3,4 로 보이므로 TC ID 순서도 함께 단언한다</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 화면의 No 컬럼</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>FE 1.4.0.0</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>FE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SYM-41</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>BUG-095</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>TC 복제가 프로젝트 전체 max(no)+1 을 줘서 시트 안 번호에 구멍이 난다</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>- 시트 안에서 1 부터 이어지던 번호가 복제 뒤 갑자기 다른 시트의 최대값 다음으로 뛴다
+- 프로젝트 118 의 결제 시트: 1, 2, 3 다음 복제본이 51</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>- no 는 시트 안 순번이다. 결제 시트의 최대가 3 이면 복제본은 4 여야 한다</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>- 다른 시트(로그인, 최대 50)의 번호가 따라와 51 이 붙었다</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>1. 시트 둘을 만들고 각각 no 를 1 부터 매긴다
+2. 번호가 작은 쪽 시트의 TC 를 복제한다
+3. 새 TC 의 no 를 본다</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>- 실 DB: 프로젝트 118 결제 시트에 no 4, 5, 6, 51
+- 재현 테스트에서 결제 시트 복제본이 4 가 아니라 501</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>원인: - testcases.py 의 clone 과 bulk-clone 이 max(no) 를 프로젝트 전체에서 구했다
+- 신규 행 추가(프론트가 그 시트의 max+1 을 보낸다)와 엑셀 임포트(no_offset=0)는 시트 기준이라 복제만 규약을 어겼다
+수정 내용: - _max_no_in_sheet 헬퍼를 두고 두 복제 경로가 시트 기준 max+1 을 쓰게 했다
+- bulk-clone 은 시트별 카운터를 캐시해 같은 시트 다건 복제에서 번호가 겹치지 않는다
+- max 를 구할 때 지운 TC 도 센다. 삭제는 soft delete 라, 살아 있는 것만 보면 지운 번호를 복제가 다시 쓰고 복원하는 순간 같은 시트에 같은 번호가 둘이 된다</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>- test_tc_clone_numbering.py 5건. 단건/일괄 복제, 다른 시트의 큰 번호 무시, 지운 TC 번호 재사용 금지까지 본다</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>- TC 복제로 만들어지는 새 TC 의 no. 이미 만들어진 TC 는 그대로다</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>BE 1.4.0.0</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>BE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SYM-42</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>BUG-096</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>수행 이름에 한글이 있으면 엑셀 내보내기가 500 이다</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 화면의 Excel 버튼이 실패한다</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>- 이름과 무관하게 파일이 내려와야 한다</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>- 500 Internal server error. 같은 수행을 영문 이름으로 만들면 200</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>1. 이름에 한글이 든 테스트 수행을 만든다
+2. 그 수행에서 Excel 을 누른다</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>- 같은 프로젝트에서 ASCII 이름 200, 한글 이름 500 을 나란히 실측</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>원인: - testruns.py 의 내보내기가 Content-Disposition 에 수행 이름을 그대로 넣었다. 헤더는 latin-1 만 담아서 인코딩에서 터진다
+- 리포트와 TC 목록 내보내기 3곳은 이미 RFC 5987 을 쓰고 있었고 이 한 곳만 옛 방식이었다
+수정 내용: - filename*=UTF-8'' 형식으로 맞췄다. 나머지 내보내기와 같은 모양이다</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>- test_run_export_numbering.py 가 한글 이름 수행으로 내보내기를 호출한다. 500 이면 그 자리에서 걸린다</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>- 테스트 수행 엑셀 내보내기</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>BE 1.4.0.0</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>BE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SYM-43</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>BUG-097</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>같은 수행인데 수행 엑셀과 리포트 엑셀의 No 와 행 순서가 다르다</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>- 한 수행을 두 곳에서 엑셀로 뽑으면 같은 행이 서로 다른 번호를 단다
+- 여러 시트를 담은 수행에서는 행 순서도 다르다</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>- 같은 수행이면 두 파일의 번호와 순서가 같아야 한다</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>- 수행 엑셀은 1, 2, 3, 4. 리포트 엑셀은 저장된 no 를 그대로 써서 4, 5, 6, 51</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>1. 시트가 여럿인 프로젝트에서 수행을 만든다
+2. 테스트 수행 화면에서 Excel 을 받는다
+3. 리포트 화면에서 엑셀을 받는다
+4. 두 파일의 No 컬럼을 대조한다</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>- 두 응답을 같은 수행으로 받아 행 단위로 대조한 테스트가 첫 행부터 어긋났다</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>원인: - 두 내보내기가 정렬과 번호를 각자 들고 있었다. 수행 엑셀만 고치면서 갈라졌다
+수정 내용: - services/sheet_order.py 를 만들어 두 내보내기가 같은 함수로 세우고 같은 규약으로 번호를 매긴다
+- 시트 트리가 비어 있는 옛 데이터에서도 화면과 같은 차례가 되도록 폴백을 넣었다</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>- 두 응답을 행 단위로 대조하는 테스트를 뒀다. 한쪽만 고치면 실패한다
+- 화면 시트 탭 순서와 내보내기 순서가 같은지 보는 테스트도 함께 뒀다</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>- 리포트 엑셀의 Results 시트</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>BE 1.4.0.0</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>BE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SYM-44</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>BUG-098</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>라운드가 비어 있는 수행이 하나라도 있으면 그 프로젝트의 수행 목록이 500 이다</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>- 특정 프로젝트에서 테스트 수행 탭이 '등록된 테스트 수행이 없습니다' 로 보인다. DB 에는 수행이 있다</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>- 라운드가 비어 있어도 목록에 나와야 한다</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>- GET /api/projects/116/testruns 가 500. 화면은 빈 목록으로 그린다</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>1. round 가 NULL 인 수행이 있는 프로젝트를 연다
+2. 테스트 수행 탭을 누른다</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>- 실 DB 프로젝트 116 에 round 가 NULL 인 수행 2건(25, 26)
+- 같은 서버에서 프로젝트 118 은 200, 116 은 500</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>BE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SYM-45</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>BUG-099</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>기존 TC 의 no 가 시트 안 순번 규약을 만족하지 않는다</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>- 시트 안 번호에 구멍과 중복이 남아 있다. TC 관리 화면의 시트 탭과 TC 엑셀 내보내기에 그대로 보인다</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>- no 는 시트 안에서 1 부터 이어지는 순번이다</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>- 프로젝트 118 결제 시트가 4, 5, 6, 51. 프로젝트 116 은 시트별 최소값이 1, 28, 58, 80, 104, 117, 127, 131 로 흩어져 있고 최대값이 430 대까지 간다</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>1. TC 관리에서 번호가 흩어진 시트를 연다
+2. No 컬럼을 본다</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>- 실 DB 시트별 min/max 조회 결과</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>BE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SYM-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>BUG-100</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>동시에 복제하면 같은 시트에 같은 no 가 들어갈 수 있다</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>- 같은 시트의 TC 를 두 요청이 동시에 복제하면 둘 다 같은 번호를 받을 수 있다</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>- 시트 안에서 no 는 겹치지 않아야 한다</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>- 두 요청이 같은 max(no) 를 읽고 각자 +1 을 한다. no 에 유니크 제약이 없어 DB 도 막지 않는다</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>1. 같은 시트의 TC 두 건에 대해 복제 요청을 동시에 보낸다
+2. 두 새 TC 의 no 를 본다</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>- 미확인</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>- 코드 경로만 확인했다. 실제 충돌은 재현하지 않았다. testcases.py 의 두 복제 경로가 max 조회와 삽입 사이를 잠그지 않는다</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>BE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SYM-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SEC-015</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>수행 엑셀과 리포트 엑셀에 수식 인젝션 새니타이즈가 없다</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>- TC 내용이 =, +, -, @ 로 시작하면 엑셀에서 수식으로 해석된다</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>- 세 내보내기 경로가 같은 새니타이즈를 거쳐야 한다</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>- TC 목록 내보내기(export_service.py)에만 새니타이즈가 있고 수행 엑셀과 리포트 엑셀에는 없다</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>1. 기대 결과 칸에 =1+1 로 시작하는 값을 넣는다
+2. 수행 엑셀을 받아 연다</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>- 미확인</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>- export_service.py 에 새니타이즈 함수가 있고 testruns.py, reports.py 에는 호출이 없다</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>BE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SYM-48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U162"/>
+  <dimension ref="A1:U164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12306,14 +12306,37 @@
           <t>- 코드 리뷰</t>
         </is>
       </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>원인: * 응답 스키마가 `round` 를 필수 정수로 읽는데 컬럼은 NULL 을 받았다. 목록 응답 하나가 못 만들어지면 그 프로젝트의 수행 목록 전체가 500 이 된다.
+수정 내용: * 컬럼을 NOT NULL, server_default 1 로 바꾸고 비어 있던 2건을 1 라운드로 채웠다 (alembic e5a83f21c760)
+* 응답 스키마도 옛 NULL 을 1 로 읽어 마이그레이션 전 DB 를 보는 서버에서 다시 터지지 않게 했다
+* 쓰기 쪽도 막았다. `PUT /testruns` 에 `round: null` 을 보내면 400 으로 거절한다. 전에는 커밋에서 제약에 걸려 409 가 났고 이유를 알 수 없었다</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>* `test_run_round_nullable.py` 4건. 컬럼 제약, 실제 쓰기 거부, 수정 API 거절, 옛 NULL 읽기까지 본다</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>* 테스트 수행 목록 API. 실 DB 프로젝트 116 이 열리지 않던 것이 정상으로 돌아왔다</t>
+        </is>
+      </c>
       <c r="R159" t="inlineStr">
         <is>
           <t>BE 1.4.1.0</t>
         </is>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>* BE 1.4.2.0 / DB 0.8.1.0</t>
+        </is>
+      </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -12389,14 +12412,40 @@
           <t>- 코드 리뷰</t>
         </is>
       </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>원인: * 복제가 프로젝트 전체 max(no)+1 을 주던 동안 시트 안 번호에 구멍이 쌓였다([SYM-42](https://linear.app/sym804/issue/SYM-42/bug-095-tc-복제가-프로젝트-전체-maxno1-을-줘서-시트-안-번호에-구멍이-난다)). 그 상태를 되돌리는 장치가 없었다
+수정 내용: * alembic f2b7c04e91a8 이 (project_id, sheet_name) 마다 no 를 1..N 으로 다시 매긴다. 순서는 바꾸지 않고 번호만 촏촏해진다
+* 지운 TC 는 살아 있는 번호 뒤로 민다. 그 자리에 두면 되살릴 때 겹친다
+* 순위를 CTE 가 아니라 임시 테이블에 담는다. 갱신 대상과 같은 테이블을 읽는 CTE 는 SQLite 가 인라인으로 펼치면 이미 바꾼 값 위에서 순위를 매긴다
+* 바꾸기 전 번호를 `_tc_no_backup_f2b7c04e91a8` 테이블에 남긴다. 되돌릴 수 없는 변경이라 대조할 것을 두었다</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>* 번호를 넣는 네 경로를 상위 이슈에서 모두 막았다([SYM-50](https://linear.app/sym804/issue/SYM-50/bug-102-tc-번호를-넣는-경로가-시트-안-순번-규약을-지키지-않는다)). 마이그레이션 하나로는 다음 임포트 한 번에 되돌아간다
+* `test_tc_no_normalize.py` 7건. 500행 시트로 실행 계획이 달라지는 구간까지 본다</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>* 실 DB 23개 시트 중 규약을 어기던 13개가 정리됐다. TC 총계 2172건 그대로고 순서도 유지된다
+* TC 관리 화면의 No 와 TC 목록 엑셀이 달라진다. 수행 화면과 두 엑셀은 목록 순번이라 영향이 없다</t>
+        </is>
+      </c>
       <c r="R160" t="inlineStr">
         <is>
           <t>BE 1.4.1.0</t>
         </is>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>* DB 0.8.1.0</t>
+        </is>
+      </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
@@ -12472,14 +12521,37 @@
           <t>- 코드 리뷰</t>
         </is>
       </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>원인: * 파이썬에서 max(no) 를 읽고 +1 해서 넣었다. 읽기와 쓰기 사이가 열려 있었고 제약도 없어 DB 가 막아 주지 않았다
+수정 내용: * `_next_no_expr()` 로 바꿨다. INSERT 문 안의 scalar subquery 로 세므로 그 창이 없다. SQL 로그로 INSERT 안에 SELECT 가 들어가는 것을 확인했다
+* 보장은 제약이 한다. `(project_id, sheet_name, no)` 부분 유니크 인덱스를 걸었다(a3d61f0c8be2)</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>* `test_tc_clone_concurrent.py` 2건(8병렬 복제). 다만 이 테스트는 **수정 전에도 통과했다**. SQLite 가 쓰기를 직렬화해서 실측 재현이 안 됐다
+* 즉 이 결함은 코드 경로로만 성립하고 실측으로는 못 봤다. 그래도 서브쿼리 방식은 비용이 없고 SQLite 의 직렬화에 기대지 않는 모양이라 그대로 둔다</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>* TC 복제 두 경로(단건, 일괄)</t>
+        </is>
+      </c>
       <c r="R161" t="inlineStr">
         <is>
           <t>BE 1.4.1.0</t>
         </is>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>* BE 1.4.2.0 / DB 0.8.1.0</t>
+        </is>
+      </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U161" t="inlineStr">
@@ -12555,19 +12627,267 @@
           <t>- 코드 리뷰</t>
         </is>
       </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>원인: * 새니타이즈 함수가 TC 목록 내보내기 파일 안에만 있었다. 내보내기 경로가 셋인데 한 곳에만 두면 나머지는 뜼린 채로 남는다
+수정 내용: * `services/excel_safe.py` 로 빼서 세 경로가 같은 함수를 쓴다
+* 막는 시작 문자에 줄바꿈(\n)을 더했다. OWASP 목록에는 없지만 같은 계열이고 막아서 잃을 것이 없다</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>* `test_export_formula_injection.py` 4건. 세 내보내기를 모두 보고, 막아야 하는 시작 문자를 하나도 빠뜨렸는지 함수 단위로도 본다
+* 이 테스트는 원래 CI 에서 건너뛰어지고 있었다. 가드를 고쳐 지금은 기본 조건에서 돌다([SYM-49](https://linear.app/sym804/issue/SYM-49/bug-101-테스트-40건이-ci-에서-건너뛰어지고-있었다))</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>* 수행 엑셀, 리포트 엑셀. TC 목록 내보내기는 원래 막혀 있었다</t>
+        </is>
+      </c>
       <c r="R162" t="inlineStr">
         <is>
           <t>BE 1.4.1.0</t>
         </is>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>* BE 1.4.2.0</t>
+        </is>
+      </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>미해결</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>SYM-48</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>BUG-101</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>테스트 40건이 CI 에서 건너뛰어지고 있었다</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>- 일부 테스트 파일이 CI 와 로컬 기본 실행에서 한 줄도 돌지 않는다
+- 그 안에 보안 수정(엑셀 수식 인젝션) 검증이 들어 있었다</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>- 개발 서버가 떠 있지 않으면 격리 환경이므로 전부 실행돼야 한다</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>- 기본 수집 262건, TEST_PORT 를 지정하면 302건. 40건 차이</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>1. 개발 서버를 내린다
+2. cd backend &amp;&amp; python -m pytest --collect-only -q
+3. 수집 건수를 TEST_PORT=8009 로 돌린 것과 비교한다</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>- 수집 건수 262 대 302
+- .github/workflows/ci.yml 이 TEST_PORT 도 ALLOW_DEV_DB 도 주지 않는다</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>원인: - skip 가드가 포트 번호(:8008)로 판정했다
+- 그런데 conftest 는 개발 서버가 없으면 임시 DB 를 잡고 8008 에 격리 서버를 직접 띄운다. 그 상황은 위험하지 않은데도 건너뛰었다
+수정 내용: - backend/dev_db_guard.py 를 두고 conftest 가 실제 격리 여부를 채운다
+- 8개 파일이 포트가 아니라 그 값으로 판정한다
+- from conftest import 는 tests_unit/conftest.py 가 이름을 선점해 ImportError 가 나므로 별도 모듈로 뺐다</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>- 기본 조건에서 323건이 수집되고 전부 통과하는 것을 확인했다. 다음에 같은 가드를 복사해도 포트가 아니라 격리 여부를 본다</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>- 백엔드 테스트 스위트 전체</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>BE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>BE 1.4.2.0</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SYM-49</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>BUG-102</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>TC 번호를 넣는 경로가 시트 안 순번 규약을 지키지 않는다</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>- 마이그레이션으로 번호를 1..N 으로 정리해도 다음 임포트나 드래그 한 번에 되돌아간다
+- 신규 생성, 임포트, 수정, 드래그 정렬이 각자 임의의 번호를 저장한다</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>- 살아 있는 TC 의 no 는 시트 안에서 1 부터 이어지고 겹치지 않는다</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>- 신규 생성이 클라이언트가 보낸 번호를 그대로 저장한다
+- 엑셀/CSV/마크다운 임포트가 파일의 No 를 그대로 저장한다
+- 드래그 정렬이 화면에 보이는 행만 1..N 으로 매겨 저장한다. 전체 보기면 시트 경계를 넘고, 검색 중이면 숨은 행이 빠진다
+- 수정 API 로 번호를 임의 값으로 바꿀 수 있다</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>1. 시트에 TC 를 세 건 만든다
+2. No 가 10, 20, 30 인 엑셀을 그 시트로 임포트한다
+3. TC 관리에서 그 시트의 No 를 본다</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>- 새 테스트 test_tc_no_contract.py 15건이 수정 전에 절반 이상 실패했다</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>원인: - 번호를 서버가 관리하지 않고 클라이언트와 파일에 맡겼다. 제약도 없어 DB 가 막아 주지 않았다
+수정 내용: - 신규 생성이 클라이언트의 no 를 무시하고 INSERT 문 안에서 채번한다
+- 세 임포트 경로가 끝난 뒤 시트를 1..N 으로 맞춘다(services/tc_numbering.py)
+- 드래그 정렬은 한 시트 전체를 1..N 으로 보낼 때만 받는다. 아니면 400. 갱신은 음수로 밀었다가 목표값을 쓰는 2단계다
+- 수정 API 가 번호를 받지 않는다. 시트를 옮기면 양쪽 시트를 다시 매긴다
+- (project_id, sheet_name, no) 부분 유니크 인덱스로 DB 가 강제한다
+- 화면도 시트 탭이 활성이고 검색 중이 아닐 때만 드래그를 켜고, No 는 읽기 전용이다</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>- test_tc_no_contract.py 15건이 네 경로를 모두 본다
+- 인덱스가 있으므로 코드가 새도 DB 가 거절한다</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>- TC 관리 화면의 No, TC 목록 엑셀, 임포트 결과</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>BE 1.4.1.0</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>BE 1.4.2.0 / FE 1.4.2.0 / DB 0.8.1.0</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SYM-50</t>
         </is>
       </c>
     </row>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U164"/>
+  <dimension ref="A1:U167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12891,6 +12891,305 @@
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>BUG-103</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>TC ID 가 없는 파일을 다시 임포트하면 같은 행을 두 번 갱신할 수 있다</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>- TC ID 칸이 빈 파일을 두 번 임포트하면 일부 행이 갱신되지 않고 다른 행이 두 번 갱신된다</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>- 같은 파일을 다시 넣으면 같은 행이 한 번씩 갱신돼야 한다</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>- 파일에 같은 No 가 두 번 있으면 두 행 모두 같은 TC ID 로 계산된다. 첫 임포트에서는 TC-001 과 TC-001-2 로 갈라지지만, 두 번째 임포트에서는 둘 다 TC-001 을 찾는다</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>1. TC ID 칸이 비어 있고 No 가 1, 1 인 엑셀을 만든다
+2. 빈 시트에 임포트한다
+3. 같은 파일을 한 번 더 임포트한다
+4. 시트의 TC 를 본다</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>- import_service.py 의 세 파서가 TC ID 가 없으면 파일의 No 로 TC-{no:03d} 를 만든다. 저장하는 no 는 행 순번으로 바꿨지만 이 생성 규칙은 그대로다</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>BE 1.5.0.0</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SYM-51</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>BUG-104</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>파일 안에 같은 번호가 있으면 CSV 와 마크다운 임포트가 통째로 실패한다</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>- No 가 겹치는 CSV 나 마크다운을 임포트하면 409 '데이터 제약 조건에 걸렸습니다' 로 아무것도 들어가지 않는다</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>- 파일의 번호와 무관하게 받아들이고 시트 안에서 1..N 으로 정리돼야 한다</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>- 파서가 파일의 No 를 그대로 저장해 유니크 제약에 걸린다. 엑셀만 행 순서로 붙이도록 고쳐져 있었다</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>1. No 가 1, 1 인 두 줄짜리 CSV 를 만든다
+2. 아무 프로젝트에 임포트한다</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>- 재현 테스트가 409 를 받았다. 파서 수정을 되돌리면 다시 실패한다</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>원인: - 앞 릴리즈에서 시트 안 번호 규약을 세우며 엑셀 파서만 고쳤다. CSV 와 마크다운은 파일의 No 를 int 로 바꿔 그대로 넣는다
+- 유니크 인덱스를 걸기 전에는 중복이 저장됐다가 뒤에서 정리됐는데, 인덱스를 건 뒤로는 정리 코드에 닿지 못한다
+수정 내용: - 두 파서가 파일의 No 를 차례로만 쓰고 행 순번을 저장한다
+- 임포트 앞에서 그 시트의 번호를 비켜 두는 자리를 고정 상수가 아니라 시트의 최대 절댓값보다 크게 잡는다. 상수로 두면 데이터에 그 값이 들어왔을 때 부딪친다</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>- 파일 안 중복 번호, 음수 번호, 같은 시트 두 번 임포트를 보는 테스트를 세 파일 형식마다 뒀다
+- 재번호 함수를 유니크 인덱스가 걸린 테이블에서 직접 부르는 단위 테스트 11건</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>- CSV, 마크다운 임포트</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>BE 1.5.0.0</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>BE 1.5.1.0</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SYM-52</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>BUG-105</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>개발 DB 를 지키는 테스트 가드가 실제 요청 대상을 보지 않는다</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>- 격리됐다고 판정하면서 요청은 개발 서버로 가는 조합이 있다</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>- 테스트가 실제로 요청을 보내는 곳에 개발 서버가 떠 있으면 건너뛰어야 한다</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>- 판정은 TEST_PORT 를 보는데 테스트 모듈은 TEST_BASE_URL 이 없으면 8008 로 간다. TEST_PORT=8009 만 주면 판정은 안전하다 하고 요청은 개발 서버로 간다
+- 가드가 아예 없는 HTTP 테스트도 2개 있었다</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>1. 개발 서버를 8008 에 띄운다
+2. TEST_PORT=8009 만 주고 pytest 를 돌린다
+3. 요청이 어디로 가는지 본다</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>- 테스트 모듈의 기본 주소가 리터럴 8008 이고 conftest 의 폴백은 TEST_PORT 였다</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>원인: - 판정 기준과 요청 대상이 각자 기본값을 들고 있어 조용히 갈라졌다
+수정 내용: - 기본 포트를 dev_db_guard 한 곳에 두고 conftest 가 그것을 참조한다
+- 두 값이 갈라지면 실패하는 테스트를 붙였다. 그 테스트가 가드 없는 파일 2개를 찾아냈고 거기에도 가드를 달았다</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>- test_dev_db_guard.py 가 기본 포트 일치, 가드 존재, conftest 의 폴백 참조를 대조한다. conftest 를 리터럴로 되돌리면 실패한다</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>- 백엔드 테스트 스위트</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>BE 1.5.0.0</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>BE 1.5.1.0</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SYM-53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U167"/>
+  <dimension ref="A1:U170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13190,6 +13190,283 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>BUG-106</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>대시보드 날짜 필터의 선택된 버튼 글자가 보이지 않는다</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>- 대시보드 탭 날짜 필터에서 선택 상태인 버튼의 글자가 배경에 묻혀 읽히지 않는다
+- 기본 선택이 '전체' 라서 화면을 열면 바로 보인다</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>- 선택된 버튼은 강조 배경 위에 흰 글자로 보인다
+- 다른 기간 버튼과 구분된다</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>- 글자가 보이지 않는다. computed style 은 color rgb(255,255,255), background-color rgba(0,0,0,0)
+- 버튼 자리는 테두리로만 남는다</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>1. 프로젝트를 열고 대시보드 탭으로 간다
+2. 날짜 필터 줄의 첫 버튼(전체)을 본다</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>- Playwright computed style: {"txt":"전체","color":"rgb(255, 255, 255)","bg":"rgba(0, 0, 0, 0)"}
+- 같은 줄의 7일/30일/90일 은 color rgb(26,29,35) 로 정상</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>원인: 선택 상태 버튼의 `backgroundColor` 가 `var(--primary-color)` 를 참조했다. 이 토큰은 `frontend/src/index.css` 어디에도 선언돼 있지 않다. 선언된 이름은 `--primary` 와 `--accent` 다.
+폴백 없는 미선언 `var()` 는 guaranteed-invalid value 라 그 속성 선언이 통째로 버려진다. `background-color` 는 상속되지 않으므로 initial 값인 transparent 가 되고, 같은 줄의 `color: "#fff"` 는 그대로 남아 흰 배경 위 흰 글자가 됐다.
+같은 원인으로 미선언 토큰을 참조하는 자리가 소스 전체에 9곳 있었다. `--primary-color`, `--bg-secondary`, `--bg-primary`, `--color-primary`, `--border` 다섯 종이다.
+수정 내용: * 9곳을 선언된 토큰으로 교체했다. 선택 상태는 프로젝트 관행대로 `--accent` + `#fff` 를 쓴다
+* 대시보드 날짜 필터 비활성 버튼은 `--bg-card`, 날짜 입력칸은 `--bg-input`
+* TC 이력 표의 tc_id 는 `--accent`, 얼룩 배경은 `--bg-page`, 내보내기 모달 테두리는 `--border-color`
+* 사용자 매뉴얼 코드블록은 `--bg-input`. 그 페이지의 코드 셀이 이미 쓰는 토큰이다</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>`frontend/src/test/cssTokens.test.ts` 를 붙였다. 소스의 폴백 없는 `var(--x)` 참조를 모아 `.css` 의 선언 집합과 대조한다. tsc 도 eslint 도 문자열 안을 보지 않아 이 결함은 게이트를 그대로 통과한다.
+테스트가 실제로 무는지 확인했다. 아무 파일에 `var(--deliberately-undeclared)` 를 넣으면 파일과 줄 번호를 짚어 실패하고, 줄바꿈이 끼어든 형태도 잡는다. 파일을 하나도 못 읽으면 빈 배열끼리 비교해 조용히 통과하므로 수집 개수 가드를 따로 뒀다.
+이 테스트는 node API 를 써서 타입 관할을 `tsconfig.node.json` 으로 옮겼다. `tsconfig.app.json` 은 types 를 `vite/client` 와 `vitest/globals` 로 제한해서, `src` 아래에서 fs 를 쓰면 vitest 는 통과하는데 `tsc -b` 가 죽는다.</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>대시보드 날짜 필터, TC 이력 표와 내보내기 모달, 사용자 매뉴얼 코드블록, 프로젝트 설정 입력칸. 라이트와 다크 양쪽을 브라우저 computed style 과 캡처로 확인했다.
+교차 검증에서 나온 별건 2개는 따로 뒀다. 다크 테마 선택 상태의 명암비 4.31:1 은 [SYM-55](https://linear.app/sym804/issue/SYM-55/bug-107-다크-테마에서-선택-상태-버튼과-탭의-글자-명암비가-wcag-aa-에-못-미친다), 선언되지 않은 `--danger` 폴백 3곳은 [SYM-56](https://linear.app/sym804/issue/SYM-56/enh-047-선언되지-않은-danger-토큰을-폴백으로-쓰는-자리-3곳을-토큰-체계에-넣는다) 이다.</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>FE 1.5.1.0</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>FE 1.5.1.1</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SYM-54</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>BUG-107</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>다크 테마에서 선택 상태 버튼과 탭의 글자 명암비가 WCAG AA 에 못 미친다</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>- 다크 테마의 선택 상태는 --accent(#4B7BBE) 배경에 흰 글자다
+- 이 조합의 명암비가 4.31:1 로 일반 텍스트 AA 기준 4.5:1 에 못 미친다
+- 프로젝트 탭, 시트 탭, 대시보드 날짜 필터가 모두 같은 조합을 쓴다</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>- 선택 상태 글자가 다크 테마에서도 4.5:1 이상이다</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>- 4.31:1. 라이트 테마의 --accent(#2D4A7A)는 8.85:1 로 여유가 있다</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>1. 다크 테마로 바꾼다
+2. 프로젝트 탭이나 대시보드 날짜 필터의 선택된 항목 명암비를 잰다</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>- WCAG 상대휘도 계산: #4B7BBE 대 #FFFFFF = 4.31:1
+- 참고로 --accent-hover(#3A6AAD)는 5.46:1 로 기준을 넘는다</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰 (SYM-54 교차 검증 중 Codex 지적)</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>FE 1.5.1.1</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SYM-55</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ENH-047</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>선언되지 않은 --danger 토큰을 폴백으로 쓰는 자리 3곳을 토큰 체계에 넣는다</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>- AccountRequestSection, AccountHelpPage, ResetPasswordPage 의 오류 문구가 var(--danger, #DC2626) 을 쓴다
+- --danger 는 index.css 어디에도 선언돼 있지 않아 항상 폴백 #DC2626 으로 고정된다</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>- 세 자리가 선언된 토큰을 쓰고 다크 테마에서도 테마 값을 따른다</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>- [ ] 세 자리가 선언된 토큰을 참조한다
+- [ ] 라이트와 다크에서 오류 문구 명암비가 4.5:1 이상이다</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>- 폴백이 있어 지금 깨지지는 않는다. 다만 다크 테마 토큰 체계 밖에 있어 테마를 바꿔도 색이 그대로다
+- SYM-54 가 추가한 미선언 토큰 검사는 폴백이 있는 참조를 잡지 않으므로 이 자리는 계속 남는다</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>- 폴백 있는 참조 전체를 금지하는 규칙 추가는 이번 범위가 아니다</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>FE 1.5.1.1</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>미해결</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SYM-56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U170"/>
+  <dimension ref="A1:U173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13467,6 +13467,323 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>BUG-108</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>리포트 화면이 미수행과 N/A 를 표시하지 않는다</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>- 리포트 탭의 전체 현황 카드가 전체 TC / PASS Rate / FAIL / BLOCK 네 장뿐이다.
+- 카테고리별 요약 표에 미수행 컬럼이 없어 Total 과 나머지 칸의 합이 어긋난다.
+- 대시보드와 프로젝트 목록은 결과 5종을 모두 표시하는데 리포트만 다르다.</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>- 리포트가 PASS/FAIL/BLOCK/N-A/미수행 다섯 가지를 모두 표시한다.
+- 카테고리 행마다 다섯 칸의 합이 Total 과 같다.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>- run 27(stockradar KR) 미수행 15건, run 30(stockradar_us) 미수행 134건이 화면 어디에도 나타나지 않았다.
+- run 23(ymseo_test)은 397건 중 23건만 수행했는데 PASS Rate 100% 만 보여 완료된 것처럼 읽혔다.</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>1. 미수행이 남은 런을 하나 고른다.
+2. 프로젝트 상세에서 리포트 탭을 연다.
+3. 전체 현황 카드와 카테고리별 요약 표를 확인한다.</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>- GET /api/projects/30/reports?run_id=27 응답의 not_started 는 15 인데 화면에는 없다.
+- 매뉴얼 스크린샷 16_report_tab.png(구버전)도 같은 상태를 보여준다.</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>원인: - 백엔드 report_json 은 not_started 와 not_started_rate 를 내려주고 있었으나 ReportView.tsx 가 이 값을 렌더링하지 않았다.
+- BLOCK 만 카드로 노출되어 미수행과 개념이 섞여 보였다.
+수정 내용: - 요약 카드에 PASS 건수, N/A, 미수행 카드를 추가했다.
+- 카테고리별 요약 표에 미수행 컬럼을 추가하고 N/A 셀의 하드코딩 색을 CSS 변수로 바꿨다.
+- PASS Rate 카드에 분모가 실행 건수임을 표기했다.
+- PDF Category Breakdown 표에 NA, NS 컬럼을 추가했다.</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>- ReportView 테스트 3건 추가(카드 표시, 합계 일치, 카테고리 컬럼). 고의 결함 주입으로 실제 검출되는지 확인했다.
+- 회귀 체크리스트에 TC-RPT-007/008/009 추가.</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>- 리포트 탭 화면, PDF 리포트의 카테고리 표, 사용자 매뉴얼 12절.</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>FE 1.5.1.1</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SYM-57</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>BUG-109</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>결과값이 소문자로 저장된 행 107건이 집계에서 통째로 빠진다</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>- 특정 런의 리포트와 대시보드에서 PASS/FAIL/BLOCK/N-A/미수행이 전부 0 으로 나온다.
+- Total 만 실제 행 수를 보여주어 합이 맞지 않는다.</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>- 결과값 표기와 무관하게 집계 합이 Total 과 같다.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>- run 25 는 25건 전부, run 26 은 82건 전부가 0 으로 집계됐다.
+- 그중 BLOCK 3건은 리포트에 한 번도 나타난 적이 없다.</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>1. test_results.result 에 소문자 값이 있는 런을 고른다.
+2. 리포트 탭에서 그 런을 선택한다.
+3. 전체 현황 카드를 확인한다.</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>- SELECT test_run_id, result, COUNT(*) 결과: run 25 pass 23 / block 2, run 26 pass 80 / fail 1 / block 1.
+- 교정 전 GET reports?run_id=25 응답: total 25, pass 0, fail 0, block 0, na 0, not_started 0.</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>원인: - SQLite 는 = 비교에서 대소문자를 구분하는데 집계 쿼리가 대문자 enum 값과만 비교한다.
+- test_results.result 는 SAEnum 이지만 SQLite 에서는 create_constraint 기본값이 False 라 CHECK 제약이 걸리지 않아 임의 문자열이 들어갈 수 있었다.
+- 현재 저장 API 는 TestResultValue 로 검증해 소문자를 400 으로 막는다. 남은 107건은 검증이 붙기 전 또는 DB 직접 수정으로 들어온 과거 데이터다.
+수정 내용: - 백업 후 UPDATE test_results SET result = UPPER(result) 로 107건을 교정했다(run 25 25건, run 26 82건).
+- 교정 전후 전체 행 수 5209 로 동일, 허용값 밖 0 건을 확인했다.
+- 함께 발견된 엠대시 7건(test_results.actual_result 1건, test_cases.remarks 6건)도 하이픈으로 교체했다.</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>- 미적용. SQLite CHECK 제약(create_constraint=True) 마이그레이션은 DB 버전이 올라가므로 별도 이슈로 분리했다.
+- 현재 저장 경로는 enum 검증으로 막혀 있어 신규 유입 경로는 없다.</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>- 토스증권 웹 QA 프로젝트의 run 25, run 26 리포트와 대시보드 통계.</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>DB 0.9.0.0</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SYM-58</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>BUG-110</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>푸터 버전 문구가 실제 릴리즈 버전과 다르다</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>- 모든 화면 하단 푸터가 YM TestCase v1.3.3.0 으로 표시된다.</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>- 푸터가 현재 릴리즈 버전을 보여준다.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>- 릴리즈 노트 기준 System 1.5.1.1 인데 푸터는 1.3.3.0 이다. 여덟 번의 릴리즈 동안 갱신되지 않았다.</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>1. 아무 화면이나 연다.
+2. 화면 하단 푸터 문구를 확인한다.</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>- frontend/src/i18n/ko/common.json 과 en/common.json 의 version 키 값이 v1.3.3.0 이다.</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>원인: - 버전 문구가 i18n 문자열에 하드코딩되어 있고 릴리즈 절차에 갱신 단계가 없다.
+수정 내용: - ko/en common.json 의 version 을 v1.5.2.0 으로 갱신했다.</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>- 미적용. package.json 또는 단일 소스에서 주입하는 구조 변경은 별도 이슈로 둔다.</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>- 전 화면 푸터 문구.</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>FE 1.5.1.1</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SYM-59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U173"/>
+  <dimension ref="A1:U175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13784,6 +13784,214 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>BUG-111</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>TC 가 없는 프로젝트에서 시트 분리 내보내기가 500 으로 실패한다</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>- TC 관리 탭의 Excel Export 에서 시트 분리를 고르면 오류 토스트만 뜨고 파일이 내려오지 않는다.
+- 시트 통합으로 고르면 정상으로 내려온다.</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>- 두 모드 모두 파일이 내려온다. TC 가 없으면 헤더만 있는 파일이 나온다.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>- GET /api/projects/19/testcases/export?split_sheets=true 가 500 과 Internal server error 를 낸다.</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>1. TC 가 한 건도 없는 프로젝트를 연다.
+2. TC 관리 탭에서 Excel Export 를 누른다.
+3. 시트 분리 (시트별 탭) 를 고르고 다운로드를 누른다.</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>- IndexError: At least one sheet must be visible (openpyxl/workbook/_writer.py:35)
+- 같은 프로젝트에서 split_sheets=false 는 200 / 5454 bytes.</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>- 사용자</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>원인: - export_service 가 wb.remove(wb.active) 로 기본 시트를 지운 뒤 TC 의 sheet_name 별로 탭을 만든다.
+- TC 가 0건이면 sheets_map 이 비어 탭이 하나도 생기지 않고, 시트 0개인 워크북은 저장 단계에서 죽는다.
+- 전체 TC 가 소프트 삭제된 프로젝트도 조회 결과가 빈 목록이라 같은 경로를 탄다.
+수정 내용: - sheets_map 이 비면 Test Cases 한 장을 넣어 통합 모드와 같은 결과를 낸다.
+- 시트명 정제를 _safe_sheet_title 헬퍼로 모으고 31자 상한과 중복 회피를 함께 처리한다.</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>- backend/test_export_empty_project.py 5건 추가. 고의 결함 주입으로 검출 여부를 확인했다.
+- 회귀 체크리스트에 TC-EXP-001/002/003 추가.</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>- TC 목록 엑셀 내보내기의 시트 분리 모드. 런 엑셀과 리포트 엑셀은 시트를 항상 만들어 해당 없음.</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>BE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>SYM-60</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>BUG-112</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>시트명이 31자를 넘고 서로 겹치면 엑셀 탭 이름이 32자가 된다</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>- 시트 분리로 내보낸 파일의 탭 이름이 엑셀 상한인 31자를 넘는다.</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>- 모든 탭 이름이 31자 이하이고 서로 겹치지 않는다.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>- 앞 31자가 같은 시트 두 개를 만들어 내보내니 탭 이름이 32자로 나왔다.</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>1. 앞 31자가 같고 뒤만 다른 시트 두 개를 만든다.
+2. 각 시트에 TC 를 한 건씩 넣는다.
+3. 시트 분리로 내보내고 탭 이름 길이를 확인한다.</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>- 항상</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>- 탭 이름 길이 실측: [5, 3, 4, 31, 32]. 마지막 항목이 상한을 넘는다.</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>- 코드 리뷰</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>원인: - 정제 전에 31자로 자르기 때문에 앞부분이 같은 이름끼리 충돌한다.
+- openpyxl 은 중복 제목을 만나면 뒤에 번호를 붙이는데 그 번호가 상한 밖으로 나간다.
+수정 내용: - _safe_sheet_title 이 정제와 자르기를 한 자리에서 하고, 충돌하면 번호까지 포함해 31자 안에 넣는다.
+- 금지 문자만 남아 이름이 비면 기본 으로 채운다.</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>- test_export_empty_project.py 에 31자 상한과 금지 문자 케이스 테스트 추가.</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>- TC 목록 엑셀 내보내기의 시트 분리 모드. 기존 프로젝트 9개 탭 이름은 수정 전후 동일하다.</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>BE 1.5.2.0</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SYM-61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Issue_list.xlsx
+++ b/Issue_list.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U175"/>
+  <dimension ref="A1:U176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13992,6 +13992,98 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ENH-048</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>로컬 구동과 API 호출을 devctl 한 자리로 모은다</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>- 서버를 띄울 때마다 uvicorn 명령을 손으로 조립한다.
+- 인증이 필요한 API 를 부르려면 로그인, 토큰 추출, curl 조립을 매번 반복한다.
+- run_dev.sh 는 포그라운드로 잡고 Ctrl+C 를 기다려 자동화에서 쓸 수 없다.</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>- scripts/devctl.py 의 up, down, status, token, api 로 끝난다.
+- up 이 기존 프로세스를 먼저 정리하므로 옛 코드가 응답하는 사고가 나지 않는다.
+- .claude/skills/dev 에 포트, DB 위치, 브라우저 확인 절차, 함정을 적어 둔다.</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>- [x] up, down, status, token, api 가 모두 동작한다
+- [x] 포트를 LISTEN 하는 PID 만 종료한다
+- [x] 비밀번호가 코드에 없다
+- [x] 프로젝트 스킬이 레포에 추적된다</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>- 한 번의 작업에서 로그인과 토큰 조립을 여섯 번 넘게 반복했다.
+- 그 과정에서 실제로 두 번 틀렸다. 옛 uvicorn 이 살아 있어 수정 전 코드가 응답했고, 프론트 PID 를 못 찾아 서버가 내려간 줄 알고 방치했다.</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>- devctl.py 추가, .claude/skills/dev/SKILL.md 추가, .gitignore 에서 프로젝트 스킬만 추적하도록 예외 지정.
+- Git Bash 의 경로 변환과 vite 의 IPv6 바인딩을 도구가 흡수한다.</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>- 다른 프로젝트로 일반화. ym-testcase 에서 쓸모를 확인한 뒤에 판단한다.
+- run_dev.sh 대체. 사람이 터미널에서 쓰는 용도는 그대로 둔다.</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>- 개발 편의 도구. 제품 런타임 코드는 바뀌지 않는다.</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>BE 1.5.3.0</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SYM-62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
